--- a/contest19_oubo (1).xlsx
+++ b/contest19_oubo (1).xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\UE_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -916,7 +916,7 @@
   </si>
   <si>
     <t>本作品はロープアクションを駆使しギミックの多いダンジョンを攻略する3Dアクションゲームとなっております。
-ロープを使ったスイングの爽快感やギミックをクリアできたときの達成感がこのゲームの魅力になります。
+ロープを使ったアクションやギミックが特徴です。
 操作もシンプルで特別なコマンドなどもないのでアクションゲームが苦手という方でも楽しめるかなと思います。</t>
     <rPh sb="0" eb="3">
       <t>ホンサクヒン</t>
@@ -933,31 +933,25 @@
     <rPh sb="57" eb="58">
       <t>ツカ</t>
     </rPh>
-    <rPh sb="65" eb="68">
-      <t>ソウカイカン</t>
-    </rPh>
-    <rPh sb="83" eb="86">
-      <t>タッセイカン</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>ミリョク</t>
-    </rPh>
-    <rPh sb="102" eb="104">
+    <rPh sb="71" eb="73">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
       <t>ソウサ</t>
     </rPh>
-    <rPh sb="110" eb="112">
+    <rPh sb="85" eb="87">
       <t>トクベツ</t>
     </rPh>
-    <rPh sb="133" eb="135">
+    <rPh sb="108" eb="110">
       <t>ニガテ</t>
     </rPh>
-    <rPh sb="138" eb="139">
+    <rPh sb="113" eb="114">
       <t>カタ</t>
     </rPh>
-    <rPh sb="141" eb="142">
+    <rPh sb="116" eb="117">
       <t>タノ</t>
     </rPh>
-    <rPh sb="148" eb="149">
+    <rPh sb="123" eb="124">
       <t>オモ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2069,18 +2063,531 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2088,518 +2595,62 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2607,15 +2658,71 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2625,121 +2732,8 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3691,18 +3685,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="187"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:22" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3719,17 +3713,17 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
-      <c r="M2" s="188" t="s">
+      <c r="M2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="189"/>
-      <c r="O2" s="189"/>
-      <c r="P2" s="189"/>
-      <c r="Q2" s="190"/>
-      <c r="S2" s="191"/>
-      <c r="T2" s="192"/>
-      <c r="U2" s="192"/>
-      <c r="V2" s="193"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="63"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="66"/>
     </row>
     <row r="3" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
@@ -3754,26 +3748,26 @@
       <c r="V3" s="11"/>
     </row>
     <row r="4" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="N4" s="194" t="s">
+      <c r="N4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="194"/>
-      <c r="P4" s="194"/>
-      <c r="Q4" s="194"/>
-      <c r="R4" s="194"/>
-      <c r="S4" s="194"/>
-      <c r="T4" s="194"/>
-      <c r="U4" s="194"/>
-      <c r="V4" s="194"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
     </row>
     <row r="5" spans="1:22" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="195" t="s">
+      <c r="A5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="204"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="77"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -3793,11 +3787,11 @@
       <c r="V5" s="3"/>
     </row>
     <row r="6" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="198"/>
-      <c r="B6" s="199"/>
-      <c r="C6" s="199"/>
-      <c r="D6" s="200"/>
-      <c r="E6" s="205"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="78"/>
       <c r="F6" s="13" t="s">
         <v>5</v>
       </c>
@@ -3807,661 +3801,661 @@
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
-      <c r="M6" s="210" t="s">
+      <c r="M6" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="210"/>
-      <c r="O6" s="211"/>
-      <c r="P6" s="211"/>
-      <c r="Q6" s="211"/>
-      <c r="R6" s="211"/>
-      <c r="S6" s="211"/>
-      <c r="T6" s="211"/>
-      <c r="U6" s="211"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="84"/>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="84"/>
+      <c r="S6" s="84"/>
+      <c r="T6" s="84"/>
+      <c r="U6" s="84"/>
       <c r="V6" s="4"/>
     </row>
     <row r="7" spans="1:22" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="198"/>
-      <c r="B7" s="199"/>
-      <c r="C7" s="199"/>
-      <c r="D7" s="200"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="73"/>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
       <c r="G7" s="15"/>
-      <c r="H7" s="206"/>
-      <c r="I7" s="208"/>
-      <c r="J7" s="208"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
       <c r="K7" s="17"/>
       <c r="L7" s="18"/>
-      <c r="M7" s="214" t="s">
+      <c r="M7" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="214"/>
-      <c r="O7" s="212"/>
-      <c r="P7" s="212"/>
-      <c r="Q7" s="212"/>
-      <c r="R7" s="212"/>
-      <c r="S7" s="212"/>
-      <c r="T7" s="212"/>
-      <c r="U7" s="212"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="85"/>
+      <c r="R7" s="85"/>
+      <c r="S7" s="85"/>
+      <c r="T7" s="85"/>
+      <c r="U7" s="85"/>
       <c r="V7" s="19"/>
     </row>
     <row r="8" spans="1:22" ht="19" x14ac:dyDescent="0.2">
-      <c r="A8" s="198"/>
-      <c r="B8" s="199"/>
-      <c r="C8" s="199"/>
-      <c r="D8" s="200"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="73"/>
       <c r="E8" s="5"/>
       <c r="F8" s="20" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="21"/>
-      <c r="H8" s="206"/>
-      <c r="I8" s="208"/>
-      <c r="J8" s="208"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
       <c r="L8" s="18"/>
-      <c r="M8" s="215"/>
-      <c r="N8" s="215"/>
-      <c r="O8" s="213"/>
-      <c r="P8" s="213"/>
-      <c r="Q8" s="213"/>
-      <c r="R8" s="213"/>
-      <c r="S8" s="213"/>
-      <c r="T8" s="213"/>
-      <c r="U8" s="213"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="86"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="86"/>
+      <c r="R8" s="86"/>
+      <c r="S8" s="86"/>
+      <c r="T8" s="86"/>
+      <c r="U8" s="86"/>
       <c r="V8" s="19"/>
     </row>
     <row r="9" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="201"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-      <c r="D9" s="203"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="76"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
-      <c r="H9" s="207"/>
-      <c r="I9" s="209"/>
-      <c r="J9" s="209"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
       <c r="K9" s="23" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="22"/>
-      <c r="M9" s="216" t="s">
+      <c r="M9" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="216"/>
-      <c r="O9" s="216"/>
-      <c r="P9" s="216"/>
-      <c r="Q9" s="216"/>
-      <c r="R9" s="216"/>
-      <c r="S9" s="216"/>
-      <c r="T9" s="216"/>
-      <c r="U9" s="216"/>
+      <c r="N9" s="89"/>
+      <c r="O9" s="89"/>
+      <c r="P9" s="89"/>
+      <c r="Q9" s="89"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89"/>
+      <c r="T9" s="89"/>
+      <c r="U9" s="89"/>
       <c r="V9" s="42"/>
     </row>
     <row r="10" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="162"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="170" t="s">
+      <c r="B10" s="115"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="171"/>
-      <c r="G10" s="172" t="s">
+      <c r="F10" s="124"/>
+      <c r="G10" s="125" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="172"/>
-      <c r="I10" s="172"/>
-      <c r="J10" s="172"/>
-      <c r="K10" s="172"/>
-      <c r="L10" s="172"/>
-      <c r="M10" s="172"/>
-      <c r="N10" s="172"/>
-      <c r="O10" s="172"/>
-      <c r="P10" s="172"/>
-      <c r="Q10" s="173"/>
-      <c r="R10" s="174" t="s">
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="125"/>
+      <c r="P10" s="125"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="S10" s="175"/>
-      <c r="T10" s="180">
+      <c r="S10" s="128"/>
+      <c r="T10" s="133">
         <v>20</v>
       </c>
-      <c r="U10" s="180"/>
+      <c r="U10" s="133"/>
       <c r="V10" s="24"/>
     </row>
     <row r="11" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="164"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="166"/>
-      <c r="E11" s="182" t="s">
+      <c r="A11" s="117"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="183"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="183"/>
-      <c r="K11" s="183"/>
-      <c r="L11" s="183"/>
-      <c r="M11" s="183"/>
-      <c r="N11" s="183"/>
-      <c r="O11" s="183"/>
-      <c r="P11" s="183"/>
-      <c r="Q11" s="184"/>
-      <c r="R11" s="176"/>
-      <c r="S11" s="177"/>
-      <c r="T11" s="92"/>
-      <c r="U11" s="92"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="138"/>
+      <c r="R11" s="129"/>
+      <c r="S11" s="130"/>
+      <c r="T11" s="134"/>
+      <c r="U11" s="134"/>
       <c r="V11" s="19"/>
     </row>
     <row r="12" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="164"/>
-      <c r="B12" s="165"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="185"/>
-      <c r="R12" s="176"/>
-      <c r="S12" s="177"/>
-      <c r="T12" s="92"/>
-      <c r="U12" s="92"/>
+      <c r="A12" s="117"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="140"/>
+      <c r="L12" s="140"/>
+      <c r="M12" s="140"/>
+      <c r="N12" s="140"/>
+      <c r="O12" s="140"/>
+      <c r="P12" s="140"/>
+      <c r="Q12" s="141"/>
+      <c r="R12" s="129"/>
+      <c r="S12" s="130"/>
+      <c r="T12" s="134"/>
+      <c r="U12" s="134"/>
       <c r="V12" s="19"/>
     </row>
     <row r="13" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="164"/>
-      <c r="B13" s="165"/>
-      <c r="C13" s="165"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="185"/>
-      <c r="R13" s="176"/>
-      <c r="S13" s="177"/>
-      <c r="T13" s="92"/>
-      <c r="U13" s="92"/>
+      <c r="A13" s="117"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="140"/>
+      <c r="J13" s="140"/>
+      <c r="K13" s="140"/>
+      <c r="L13" s="140"/>
+      <c r="M13" s="140"/>
+      <c r="N13" s="140"/>
+      <c r="O13" s="140"/>
+      <c r="P13" s="140"/>
+      <c r="Q13" s="141"/>
+      <c r="R13" s="129"/>
+      <c r="S13" s="130"/>
+      <c r="T13" s="134"/>
+      <c r="U13" s="134"/>
       <c r="V13" s="25"/>
     </row>
     <row r="14" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="164"/>
-      <c r="B14" s="165"/>
-      <c r="C14" s="165"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="185"/>
-      <c r="R14" s="176"/>
-      <c r="S14" s="177"/>
-      <c r="T14" s="92"/>
-      <c r="U14" s="92"/>
-      <c r="V14" s="144" t="s">
+      <c r="A14" s="117"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="140"/>
+      <c r="N14" s="140"/>
+      <c r="O14" s="140"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="141"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="130"/>
+      <c r="T14" s="134"/>
+      <c r="U14" s="134"/>
+      <c r="V14" s="90" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="167"/>
-      <c r="B15" s="168"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="169"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="186"/>
-      <c r="R15" s="178"/>
-      <c r="S15" s="179"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="181"/>
-      <c r="V15" s="145"/>
+      <c r="A15" s="120"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="143"/>
+      <c r="L15" s="143"/>
+      <c r="M15" s="143"/>
+      <c r="N15" s="143"/>
+      <c r="O15" s="143"/>
+      <c r="P15" s="143"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="131"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="135"/>
+      <c r="U15" s="135"/>
+      <c r="V15" s="91"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="150" t="s">
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="151"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="151"/>
-      <c r="L16" s="151"/>
-      <c r="M16" s="151"/>
-      <c r="N16" s="151"/>
-      <c r="O16" s="151"/>
-      <c r="P16" s="151"/>
-      <c r="Q16" s="151"/>
-      <c r="R16" s="151"/>
-      <c r="S16" s="151"/>
-      <c r="T16" s="151"/>
-      <c r="U16" s="151"/>
-      <c r="V16" s="152"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="102"/>
+      <c r="L16" s="102"/>
+      <c r="M16" s="102"/>
+      <c r="N16" s="102"/>
+      <c r="O16" s="102"/>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="102"/>
+      <c r="R16" s="102"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="102"/>
+      <c r="U16" s="102"/>
+      <c r="V16" s="103"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" s="125"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="154"/>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="154"/>
-      <c r="J17" s="154"/>
-      <c r="K17" s="154"/>
-      <c r="L17" s="154"/>
-      <c r="M17" s="154"/>
-      <c r="N17" s="154"/>
-      <c r="O17" s="154"/>
-      <c r="P17" s="154"/>
-      <c r="Q17" s="154"/>
-      <c r="R17" s="154"/>
-      <c r="S17" s="154"/>
-      <c r="T17" s="154"/>
-      <c r="U17" s="154"/>
-      <c r="V17" s="155"/>
+      <c r="A17" s="95"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
+      <c r="L17" s="105"/>
+      <c r="M17" s="105"/>
+      <c r="N17" s="105"/>
+      <c r="O17" s="105"/>
+      <c r="P17" s="105"/>
+      <c r="Q17" s="105"/>
+      <c r="R17" s="105"/>
+      <c r="S17" s="105"/>
+      <c r="T17" s="105"/>
+      <c r="U17" s="105"/>
+      <c r="V17" s="106"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="125"/>
-      <c r="B18" s="126"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="153"/>
-      <c r="F18" s="154"/>
-      <c r="G18" s="154"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="154"/>
-      <c r="J18" s="154"/>
-      <c r="K18" s="154"/>
-      <c r="L18" s="154"/>
-      <c r="M18" s="154"/>
-      <c r="N18" s="154"/>
-      <c r="O18" s="154"/>
-      <c r="P18" s="154"/>
-      <c r="Q18" s="154"/>
-      <c r="R18" s="154"/>
-      <c r="S18" s="154"/>
-      <c r="T18" s="154"/>
-      <c r="U18" s="154"/>
-      <c r="V18" s="155"/>
+      <c r="A18" s="95"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105"/>
+      <c r="M18" s="105"/>
+      <c r="N18" s="105"/>
+      <c r="O18" s="105"/>
+      <c r="P18" s="105"/>
+      <c r="Q18" s="105"/>
+      <c r="R18" s="105"/>
+      <c r="S18" s="105"/>
+      <c r="T18" s="105"/>
+      <c r="U18" s="105"/>
+      <c r="V18" s="106"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" s="125"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="153"/>
-      <c r="F19" s="154"/>
-      <c r="G19" s="154"/>
-      <c r="H19" s="154"/>
-      <c r="I19" s="154"/>
-      <c r="J19" s="154"/>
-      <c r="K19" s="154"/>
-      <c r="L19" s="154"/>
-      <c r="M19" s="154"/>
-      <c r="N19" s="154"/>
-      <c r="O19" s="154"/>
-      <c r="P19" s="154"/>
-      <c r="Q19" s="154"/>
-      <c r="R19" s="154"/>
-      <c r="S19" s="154"/>
-      <c r="T19" s="154"/>
-      <c r="U19" s="154"/>
-      <c r="V19" s="155"/>
+      <c r="A19" s="95"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="105"/>
+      <c r="M19" s="105"/>
+      <c r="N19" s="105"/>
+      <c r="O19" s="105"/>
+      <c r="P19" s="105"/>
+      <c r="Q19" s="105"/>
+      <c r="R19" s="105"/>
+      <c r="S19" s="105"/>
+      <c r="T19" s="105"/>
+      <c r="U19" s="105"/>
+      <c r="V19" s="106"/>
     </row>
     <row r="20" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="147"/>
-      <c r="B20" s="148"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="156"/>
-      <c r="F20" s="157"/>
-      <c r="G20" s="157"/>
-      <c r="H20" s="157"/>
-      <c r="I20" s="157"/>
-      <c r="J20" s="157"/>
-      <c r="K20" s="157"/>
-      <c r="L20" s="157"/>
-      <c r="M20" s="157"/>
-      <c r="N20" s="157"/>
-      <c r="O20" s="157"/>
-      <c r="P20" s="157"/>
-      <c r="Q20" s="157"/>
-      <c r="R20" s="157"/>
-      <c r="S20" s="157"/>
-      <c r="T20" s="157"/>
-      <c r="U20" s="157"/>
-      <c r="V20" s="158"/>
+      <c r="A20" s="98"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+      <c r="N20" s="108"/>
+      <c r="O20" s="108"/>
+      <c r="P20" s="108"/>
+      <c r="Q20" s="108"/>
+      <c r="R20" s="108"/>
+      <c r="S20" s="108"/>
+      <c r="T20" s="108"/>
+      <c r="U20" s="108"/>
+      <c r="V20" s="109"/>
     </row>
     <row r="21" spans="1:22" ht="19" x14ac:dyDescent="0.2">
-      <c r="A21" s="120" t="s">
+      <c r="A21" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="121"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="124"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="94"/>
       <c r="E21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="159" t="s">
+      <c r="F21" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="159"/>
+      <c r="G21" s="112"/>
       <c r="H21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="160" t="s">
+      <c r="I21" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="J21" s="160"/>
-      <c r="K21" s="160"/>
-      <c r="L21" s="160"/>
-      <c r="M21" s="160"/>
-      <c r="N21" s="160"/>
-      <c r="O21" s="160"/>
-      <c r="P21" s="160"/>
-      <c r="Q21" s="160"/>
-      <c r="R21" s="160"/>
-      <c r="S21" s="160"/>
-      <c r="T21" s="160"/>
-      <c r="U21" s="160"/>
-      <c r="V21" s="161"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="113"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="113"/>
+      <c r="P21" s="113"/>
+      <c r="Q21" s="113"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="113"/>
+      <c r="T21" s="113"/>
+      <c r="U21" s="113"/>
+      <c r="V21" s="114"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="125"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="127"/>
-      <c r="E22" s="153" t="s">
+      <c r="A22" s="95"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="F22" s="154"/>
-      <c r="G22" s="154"/>
-      <c r="H22" s="154"/>
-      <c r="I22" s="154"/>
-      <c r="J22" s="154"/>
-      <c r="K22" s="154"/>
-      <c r="L22" s="154"/>
-      <c r="M22" s="154"/>
-      <c r="N22" s="154"/>
-      <c r="O22" s="154"/>
-      <c r="P22" s="154"/>
-      <c r="Q22" s="154"/>
-      <c r="R22" s="154"/>
-      <c r="S22" s="154"/>
-      <c r="T22" s="154"/>
-      <c r="U22" s="154"/>
-      <c r="V22" s="155"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
+      <c r="O22" s="105"/>
+      <c r="P22" s="105"/>
+      <c r="Q22" s="105"/>
+      <c r="R22" s="105"/>
+      <c r="S22" s="105"/>
+      <c r="T22" s="105"/>
+      <c r="U22" s="105"/>
+      <c r="V22" s="106"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A23" s="125"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="154"/>
-      <c r="G23" s="154"/>
-      <c r="H23" s="154"/>
-      <c r="I23" s="154"/>
-      <c r="J23" s="154"/>
-      <c r="K23" s="154"/>
-      <c r="L23" s="154"/>
-      <c r="M23" s="154"/>
-      <c r="N23" s="154"/>
-      <c r="O23" s="154"/>
-      <c r="P23" s="154"/>
-      <c r="Q23" s="154"/>
-      <c r="R23" s="154"/>
-      <c r="S23" s="154"/>
-      <c r="T23" s="154"/>
-      <c r="U23" s="154"/>
-      <c r="V23" s="155"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="105"/>
+      <c r="Q23" s="105"/>
+      <c r="R23" s="105"/>
+      <c r="S23" s="105"/>
+      <c r="T23" s="105"/>
+      <c r="U23" s="105"/>
+      <c r="V23" s="106"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="125"/>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="154"/>
-      <c r="G24" s="154"/>
-      <c r="H24" s="154"/>
-      <c r="I24" s="154"/>
-      <c r="J24" s="154"/>
-      <c r="K24" s="154"/>
-      <c r="L24" s="154"/>
-      <c r="M24" s="154"/>
-      <c r="N24" s="154"/>
-      <c r="O24" s="154"/>
-      <c r="P24" s="154"/>
-      <c r="Q24" s="154"/>
-      <c r="R24" s="154"/>
-      <c r="S24" s="154"/>
-      <c r="T24" s="154"/>
-      <c r="U24" s="154"/>
-      <c r="V24" s="155"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="105"/>
+      <c r="O24" s="105"/>
+      <c r="P24" s="105"/>
+      <c r="Q24" s="105"/>
+      <c r="R24" s="105"/>
+      <c r="S24" s="105"/>
+      <c r="T24" s="105"/>
+      <c r="U24" s="105"/>
+      <c r="V24" s="106"/>
     </row>
     <row r="25" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="147"/>
-      <c r="B25" s="148"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="156"/>
-      <c r="F25" s="157"/>
-      <c r="G25" s="157"/>
-      <c r="H25" s="157"/>
-      <c r="I25" s="157"/>
-      <c r="J25" s="157"/>
-      <c r="K25" s="157"/>
-      <c r="L25" s="157"/>
-      <c r="M25" s="157"/>
-      <c r="N25" s="157"/>
-      <c r="O25" s="157"/>
-      <c r="P25" s="157"/>
-      <c r="Q25" s="157"/>
-      <c r="R25" s="157"/>
-      <c r="S25" s="157"/>
-      <c r="T25" s="157"/>
-      <c r="U25" s="157"/>
-      <c r="V25" s="158"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="108"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="108"/>
+      <c r="N25" s="108"/>
+      <c r="O25" s="108"/>
+      <c r="P25" s="108"/>
+      <c r="Q25" s="108"/>
+      <c r="R25" s="108"/>
+      <c r="S25" s="108"/>
+      <c r="T25" s="108"/>
+      <c r="U25" s="108"/>
+      <c r="V25" s="109"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="131" t="s">
+      <c r="B26" s="111"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="94"/>
+      <c r="E26" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="132"/>
-      <c r="G26" s="134" t="s">
+      <c r="F26" s="149"/>
+      <c r="G26" s="152" t="s">
         <v>96</v>
       </c>
-      <c r="H26" s="134"/>
-      <c r="I26" s="134"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="134"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="134"/>
-      <c r="N26" s="134"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="134"/>
-      <c r="Q26" s="134"/>
-      <c r="R26" s="134"/>
+      <c r="H26" s="152"/>
+      <c r="I26" s="152"/>
+      <c r="J26" s="152"/>
+      <c r="K26" s="152"/>
+      <c r="L26" s="152"/>
+      <c r="M26" s="152"/>
+      <c r="N26" s="152"/>
+      <c r="O26" s="152"/>
+      <c r="P26" s="152"/>
+      <c r="Q26" s="152"/>
+      <c r="R26" s="152"/>
       <c r="S26" s="28"/>
       <c r="T26" s="28"/>
       <c r="U26" s="28"/>
       <c r="V26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="125"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="135"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="135"/>
-      <c r="M27" s="135"/>
-      <c r="N27" s="135"/>
-      <c r="O27" s="135"/>
-      <c r="P27" s="135"/>
-      <c r="Q27" s="135"/>
-      <c r="R27" s="135"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="151"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
+      <c r="J27" s="153"/>
+      <c r="K27" s="153"/>
+      <c r="L27" s="153"/>
+      <c r="M27" s="153"/>
+      <c r="N27" s="153"/>
+      <c r="O27" s="153"/>
+      <c r="P27" s="153"/>
+      <c r="Q27" s="153"/>
+      <c r="R27" s="153"/>
       <c r="V27" s="19"/>
     </row>
     <row r="28" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="125"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="127"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="136"/>
-      <c r="H28" s="136"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="136"/>
-      <c r="K28" s="136"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="136"/>
-      <c r="N28" s="136"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="136"/>
-      <c r="Q28" s="136"/>
-      <c r="R28" s="136"/>
+      <c r="A28" s="95"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="150"/>
+      <c r="F28" s="151"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="154"/>
+      <c r="O28" s="154"/>
+      <c r="P28" s="154"/>
+      <c r="Q28" s="154"/>
+      <c r="R28" s="154"/>
       <c r="S28" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="T28" s="137" t="s">
+      <c r="T28" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="U28" s="137"/>
+      <c r="U28" s="155"/>
       <c r="V28" s="30"/>
     </row>
     <row r="29" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="125"/>
-      <c r="B29" s="126"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="138" t="s">
+      <c r="A29" s="95"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="139"/>
-      <c r="G29" s="142" t="s">
+      <c r="F29" s="157"/>
+      <c r="G29" s="160" t="s">
         <v>97</v>
       </c>
-      <c r="H29" s="142"/>
-      <c r="I29" s="142"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="142"/>
-      <c r="M29" s="142"/>
-      <c r="N29" s="142"/>
-      <c r="O29" s="142"/>
-      <c r="P29" s="142"/>
-      <c r="Q29" s="142"/>
-      <c r="R29" s="142"/>
+      <c r="H29" s="160"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="160"/>
+      <c r="L29" s="160"/>
+      <c r="M29" s="160"/>
+      <c r="N29" s="160"/>
+      <c r="O29" s="160"/>
+      <c r="P29" s="160"/>
+      <c r="Q29" s="160"/>
+      <c r="R29" s="160"/>
       <c r="S29" s="31"/>
-      <c r="T29" s="137" t="s">
+      <c r="T29" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="U29" s="137"/>
+      <c r="U29" s="155"/>
       <c r="V29" s="30"/>
     </row>
     <row r="30" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="125"/>
-      <c r="B30" s="126"/>
-      <c r="C30" s="126"/>
-      <c r="D30" s="127"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="135"/>
-      <c r="H30" s="135"/>
-      <c r="I30" s="135"/>
-      <c r="J30" s="135"/>
-      <c r="K30" s="135"/>
-      <c r="L30" s="135"/>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
-      <c r="O30" s="135"/>
-      <c r="P30" s="135"/>
-      <c r="Q30" s="135"/>
-      <c r="R30" s="135"/>
+      <c r="A30" s="95"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
+      <c r="J30" s="153"/>
+      <c r="K30" s="153"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="153"/>
+      <c r="N30" s="153"/>
+      <c r="O30" s="153"/>
+      <c r="P30" s="153"/>
+      <c r="Q30" s="153"/>
+      <c r="R30" s="153"/>
       <c r="V30" s="19"/>
     </row>
     <row r="31" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="128"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="129"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="141"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="143"/>
-      <c r="J31" s="143"/>
-      <c r="K31" s="143"/>
-      <c r="L31" s="143"/>
-      <c r="M31" s="143"/>
-      <c r="N31" s="143"/>
-      <c r="O31" s="143"/>
-      <c r="P31" s="143"/>
-      <c r="Q31" s="143"/>
-      <c r="R31" s="143"/>
+      <c r="A31" s="145"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="161"/>
+      <c r="L31" s="161"/>
+      <c r="M31" s="161"/>
+      <c r="N31" s="161"/>
+      <c r="O31" s="161"/>
+      <c r="P31" s="161"/>
+      <c r="Q31" s="161"/>
+      <c r="R31" s="161"/>
       <c r="S31" s="32"/>
       <c r="T31" s="32"/>
       <c r="U31" s="32"/>
@@ -4469,214 +4463,214 @@
     </row>
     <row r="32" spans="1:22" ht="14" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="1:22" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="80" t="s">
+      <c r="A33" s="163" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="81"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="82"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="165"/>
       <c r="E33" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="89" t="s">
+      <c r="F33" s="172" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="89"/>
-      <c r="L33" s="89"/>
-      <c r="M33" s="89"/>
-      <c r="N33" s="89"/>
-      <c r="O33" s="89"/>
-      <c r="P33" s="89"/>
-      <c r="Q33" s="89"/>
-      <c r="R33" s="89"/>
-      <c r="S33" s="89"/>
-      <c r="T33" s="89"/>
-      <c r="U33" s="89"/>
-      <c r="V33" s="90"/>
+      <c r="G33" s="172"/>
+      <c r="H33" s="172"/>
+      <c r="I33" s="172"/>
+      <c r="J33" s="172"/>
+      <c r="K33" s="172"/>
+      <c r="L33" s="172"/>
+      <c r="M33" s="172"/>
+      <c r="N33" s="172"/>
+      <c r="O33" s="172"/>
+      <c r="P33" s="172"/>
+      <c r="Q33" s="172"/>
+      <c r="R33" s="172"/>
+      <c r="S33" s="172"/>
+      <c r="T33" s="172"/>
+      <c r="U33" s="172"/>
+      <c r="V33" s="173"/>
     </row>
     <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="83"/>
-      <c r="B34" s="84"/>
-      <c r="C34" s="84"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="91" t="s">
+      <c r="A34" s="166"/>
+      <c r="B34" s="167"/>
+      <c r="C34" s="167"/>
+      <c r="D34" s="168"/>
+      <c r="E34" s="174" t="s">
         <v>99</v>
       </c>
-      <c r="F34" s="92"/>
-      <c r="G34" s="92"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="92"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="92"/>
-      <c r="M34" s="92"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="92"/>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="92"/>
-      <c r="R34" s="92"/>
-      <c r="S34" s="92"/>
-      <c r="T34" s="92"/>
-      <c r="U34" s="92"/>
-      <c r="V34" s="93"/>
+      <c r="F34" s="134"/>
+      <c r="G34" s="134"/>
+      <c r="H34" s="134"/>
+      <c r="I34" s="134"/>
+      <c r="J34" s="134"/>
+      <c r="K34" s="134"/>
+      <c r="L34" s="134"/>
+      <c r="M34" s="134"/>
+      <c r="N34" s="134"/>
+      <c r="O34" s="134"/>
+      <c r="P34" s="134"/>
+      <c r="Q34" s="134"/>
+      <c r="R34" s="134"/>
+      <c r="S34" s="134"/>
+      <c r="T34" s="134"/>
+      <c r="U34" s="134"/>
+      <c r="V34" s="175"/>
     </row>
     <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="83"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="85"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="92"/>
-      <c r="O35" s="92"/>
-      <c r="P35" s="92"/>
-      <c r="Q35" s="92"/>
-      <c r="R35" s="92"/>
-      <c r="S35" s="92"/>
-      <c r="T35" s="92"/>
-      <c r="U35" s="92"/>
-      <c r="V35" s="93"/>
+      <c r="A35" s="166"/>
+      <c r="B35" s="167"/>
+      <c r="C35" s="167"/>
+      <c r="D35" s="168"/>
+      <c r="E35" s="174"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="134"/>
+      <c r="H35" s="134"/>
+      <c r="I35" s="134"/>
+      <c r="J35" s="134"/>
+      <c r="K35" s="134"/>
+      <c r="L35" s="134"/>
+      <c r="M35" s="134"/>
+      <c r="N35" s="134"/>
+      <c r="O35" s="134"/>
+      <c r="P35" s="134"/>
+      <c r="Q35" s="134"/>
+      <c r="R35" s="134"/>
+      <c r="S35" s="134"/>
+      <c r="T35" s="134"/>
+      <c r="U35" s="134"/>
+      <c r="V35" s="175"/>
     </row>
     <row r="36" spans="1:22" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
-      <c r="B36" s="84"/>
-      <c r="C36" s="84"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="92"/>
-      <c r="G36" s="92"/>
-      <c r="H36" s="92"/>
-      <c r="I36" s="92"/>
-      <c r="J36" s="92"/>
-      <c r="K36" s="92"/>
-      <c r="L36" s="92"/>
-      <c r="M36" s="92"/>
-      <c r="N36" s="92"/>
-      <c r="O36" s="92"/>
-      <c r="P36" s="92"/>
-      <c r="Q36" s="92"/>
-      <c r="R36" s="92"/>
-      <c r="S36" s="92"/>
-      <c r="T36" s="92"/>
-      <c r="U36" s="92"/>
-      <c r="V36" s="93"/>
+      <c r="A36" s="166"/>
+      <c r="B36" s="167"/>
+      <c r="C36" s="167"/>
+      <c r="D36" s="168"/>
+      <c r="E36" s="174"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="134"/>
+      <c r="H36" s="134"/>
+      <c r="I36" s="134"/>
+      <c r="J36" s="134"/>
+      <c r="K36" s="134"/>
+      <c r="L36" s="134"/>
+      <c r="M36" s="134"/>
+      <c r="N36" s="134"/>
+      <c r="O36" s="134"/>
+      <c r="P36" s="134"/>
+      <c r="Q36" s="134"/>
+      <c r="R36" s="134"/>
+      <c r="S36" s="134"/>
+      <c r="T36" s="134"/>
+      <c r="U36" s="134"/>
+      <c r="V36" s="175"/>
     </row>
     <row r="37" spans="1:22" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="86"/>
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="94" t="s">
+      <c r="A37" s="169"/>
+      <c r="B37" s="170"/>
+      <c r="C37" s="170"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="176" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="95"/>
-      <c r="G37" s="96">
+      <c r="F37" s="177"/>
+      <c r="G37" s="178">
         <v>3</v>
       </c>
-      <c r="H37" s="96"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="96"/>
-      <c r="K37" s="96"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="96"/>
-      <c r="N37" s="96"/>
-      <c r="O37" s="96"/>
-      <c r="P37" s="96"/>
-      <c r="Q37" s="96"/>
-      <c r="R37" s="96"/>
-      <c r="S37" s="96"/>
-      <c r="T37" s="96"/>
-      <c r="U37" s="97" t="s">
+      <c r="H37" s="178"/>
+      <c r="I37" s="178"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="178"/>
+      <c r="L37" s="178"/>
+      <c r="M37" s="178"/>
+      <c r="N37" s="178"/>
+      <c r="O37" s="178"/>
+      <c r="P37" s="178"/>
+      <c r="Q37" s="178"/>
+      <c r="R37" s="178"/>
+      <c r="S37" s="178"/>
+      <c r="T37" s="178"/>
+      <c r="U37" s="179" t="s">
         <v>26</v>
       </c>
-      <c r="V37" s="98"/>
+      <c r="V37" s="180"/>
     </row>
     <row r="38" spans="1:22" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A38" s="120" t="s">
+      <c r="A38" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="121"/>
-      <c r="C38" s="122"/>
-      <c r="D38" s="123"/>
+      <c r="B38" s="111"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="202"/>
       <c r="E38" s="35" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="36"/>
       <c r="G38" s="28"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="66"/>
-      <c r="K38" s="66"/>
-      <c r="L38" s="66"/>
-      <c r="M38" s="66"/>
-      <c r="N38" s="66"/>
-      <c r="O38" s="66"/>
-      <c r="P38" s="66"/>
-      <c r="Q38" s="66"/>
-      <c r="R38" s="66"/>
-      <c r="S38" s="66"/>
-      <c r="T38" s="66"/>
-      <c r="U38" s="66"/>
-      <c r="V38" s="67"/>
+      <c r="H38" s="203"/>
+      <c r="I38" s="203"/>
+      <c r="J38" s="203"/>
+      <c r="K38" s="203"/>
+      <c r="L38" s="203"/>
+      <c r="M38" s="203"/>
+      <c r="N38" s="203"/>
+      <c r="O38" s="203"/>
+      <c r="P38" s="203"/>
+      <c r="Q38" s="203"/>
+      <c r="R38" s="203"/>
+      <c r="S38" s="203"/>
+      <c r="T38" s="203"/>
+      <c r="U38" s="203"/>
+      <c r="V38" s="204"/>
     </row>
     <row r="39" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="83"/>
-      <c r="B39" s="84"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="85"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="69"/>
-      <c r="M39" s="69"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="69"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="69"/>
-      <c r="R39" s="69"/>
-      <c r="S39" s="69"/>
-      <c r="T39" s="69"/>
-      <c r="U39" s="69"/>
-      <c r="V39" s="70"/>
+      <c r="A39" s="166"/>
+      <c r="B39" s="167"/>
+      <c r="C39" s="167"/>
+      <c r="D39" s="168"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="140"/>
+      <c r="K39" s="140"/>
+      <c r="L39" s="140"/>
+      <c r="M39" s="140"/>
+      <c r="N39" s="140"/>
+      <c r="O39" s="140"/>
+      <c r="P39" s="140"/>
+      <c r="Q39" s="140"/>
+      <c r="R39" s="140"/>
+      <c r="S39" s="140"/>
+      <c r="T39" s="140"/>
+      <c r="U39" s="140"/>
+      <c r="V39" s="205"/>
     </row>
     <row r="40" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="86"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="72"/>
-      <c r="M40" s="72"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="72"/>
-      <c r="P40" s="72"/>
-      <c r="Q40" s="72"/>
-      <c r="R40" s="72"/>
-      <c r="S40" s="72"/>
-      <c r="T40" s="72"/>
-      <c r="U40" s="72"/>
-      <c r="V40" s="73"/>
+      <c r="A40" s="169"/>
+      <c r="B40" s="170"/>
+      <c r="C40" s="170"/>
+      <c r="D40" s="171"/>
+      <c r="E40" s="142"/>
+      <c r="F40" s="143"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="143"/>
+      <c r="I40" s="143"/>
+      <c r="J40" s="143"/>
+      <c r="K40" s="143"/>
+      <c r="L40" s="143"/>
+      <c r="M40" s="143"/>
+      <c r="N40" s="143"/>
+      <c r="O40" s="143"/>
+      <c r="P40" s="143"/>
+      <c r="Q40" s="143"/>
+      <c r="R40" s="143"/>
+      <c r="S40" s="143"/>
+      <c r="T40" s="143"/>
+      <c r="U40" s="143"/>
+      <c r="V40" s="206"/>
     </row>
     <row r="41" spans="1:22" ht="23.5" x14ac:dyDescent="0.2">
       <c r="A41" s="37" t="s">
@@ -4737,27 +4731,27 @@
       <c r="B43" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="74" t="s">
+      <c r="C43" s="207" t="s">
         <v>89</v>
       </c>
-      <c r="D43" s="74"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="74"/>
-      <c r="H43" s="74"/>
-      <c r="I43" s="74"/>
-      <c r="J43" s="74"/>
-      <c r="K43" s="74"/>
-      <c r="L43" s="74"/>
-      <c r="M43" s="74"/>
-      <c r="N43" s="74"/>
-      <c r="O43" s="74"/>
-      <c r="P43" s="74"/>
-      <c r="Q43" s="74"/>
-      <c r="R43" s="74"/>
-      <c r="S43" s="74"/>
-      <c r="T43" s="74"/>
-      <c r="U43" s="74"/>
+      <c r="D43" s="207"/>
+      <c r="E43" s="207"/>
+      <c r="F43" s="207"/>
+      <c r="G43" s="207"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="207"/>
+      <c r="J43" s="207"/>
+      <c r="K43" s="207"/>
+      <c r="L43" s="207"/>
+      <c r="M43" s="207"/>
+      <c r="N43" s="207"/>
+      <c r="O43" s="207"/>
+      <c r="P43" s="207"/>
+      <c r="Q43" s="207"/>
+      <c r="R43" s="207"/>
+      <c r="S43" s="207"/>
+      <c r="T43" s="207"/>
+      <c r="U43" s="207"/>
       <c r="V43" s="53" t="s">
         <v>32</v>
       </c>
@@ -4871,238 +4865,238 @@
       <c r="V46" s="54"/>
     </row>
     <row r="47" spans="1:22" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="75" t="s">
+      <c r="A47" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="76"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="77" t="s">
+      <c r="B47" s="209"/>
+      <c r="C47" s="209"/>
+      <c r="D47" s="209"/>
+      <c r="E47" s="210" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="78"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="78"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="78"/>
-      <c r="O47" s="78"/>
-      <c r="P47" s="78"/>
-      <c r="Q47" s="78"/>
-      <c r="R47" s="78"/>
-      <c r="S47" s="78"/>
-      <c r="T47" s="78"/>
-      <c r="U47" s="78"/>
-      <c r="V47" s="79"/>
+      <c r="F47" s="211"/>
+      <c r="G47" s="211"/>
+      <c r="H47" s="211"/>
+      <c r="I47" s="211"/>
+      <c r="J47" s="211"/>
+      <c r="K47" s="211"/>
+      <c r="L47" s="211"/>
+      <c r="M47" s="211"/>
+      <c r="N47" s="211"/>
+      <c r="O47" s="211"/>
+      <c r="P47" s="211"/>
+      <c r="Q47" s="211"/>
+      <c r="R47" s="211"/>
+      <c r="S47" s="211"/>
+      <c r="T47" s="211"/>
+      <c r="U47" s="211"/>
+      <c r="V47" s="212"/>
     </row>
     <row r="48" spans="1:22" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="99" t="s">
+      <c r="A48" s="181" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="100"/>
-      <c r="C48" s="100"/>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="100"/>
-      <c r="K48" s="100"/>
-      <c r="L48" s="100"/>
-      <c r="M48" s="100"/>
-      <c r="N48" s="100"/>
-      <c r="O48" s="100"/>
-      <c r="P48" s="100"/>
-      <c r="Q48" s="100"/>
-      <c r="R48" s="100"/>
-      <c r="S48" s="100"/>
-      <c r="T48" s="100"/>
-      <c r="U48" s="100"/>
-      <c r="V48" s="101"/>
+      <c r="B48" s="182"/>
+      <c r="C48" s="182"/>
+      <c r="D48" s="182"/>
+      <c r="E48" s="182"/>
+      <c r="F48" s="182"/>
+      <c r="G48" s="182"/>
+      <c r="H48" s="182"/>
+      <c r="I48" s="182"/>
+      <c r="J48" s="182"/>
+      <c r="K48" s="182"/>
+      <c r="L48" s="182"/>
+      <c r="M48" s="182"/>
+      <c r="N48" s="182"/>
+      <c r="O48" s="182"/>
+      <c r="P48" s="182"/>
+      <c r="Q48" s="182"/>
+      <c r="R48" s="182"/>
+      <c r="S48" s="182"/>
+      <c r="T48" s="182"/>
+      <c r="U48" s="182"/>
+      <c r="V48" s="183"/>
     </row>
     <row r="49" spans="1:22" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="102"/>
-      <c r="B49" s="103"/>
-      <c r="C49" s="103"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="103"/>
-      <c r="J49" s="103"/>
-      <c r="K49" s="103"/>
-      <c r="L49" s="103"/>
-      <c r="M49" s="103"/>
-      <c r="N49" s="103"/>
-      <c r="O49" s="103"/>
-      <c r="P49" s="103"/>
-      <c r="Q49" s="103"/>
-      <c r="R49" s="103"/>
-      <c r="S49" s="103"/>
-      <c r="T49" s="103"/>
-      <c r="U49" s="103"/>
-      <c r="V49" s="104"/>
+      <c r="A49" s="184"/>
+      <c r="B49" s="185"/>
+      <c r="C49" s="185"/>
+      <c r="D49" s="185"/>
+      <c r="E49" s="185"/>
+      <c r="F49" s="185"/>
+      <c r="G49" s="185"/>
+      <c r="H49" s="185"/>
+      <c r="I49" s="185"/>
+      <c r="J49" s="185"/>
+      <c r="K49" s="185"/>
+      <c r="L49" s="185"/>
+      <c r="M49" s="185"/>
+      <c r="N49" s="185"/>
+      <c r="O49" s="185"/>
+      <c r="P49" s="185"/>
+      <c r="Q49" s="185"/>
+      <c r="R49" s="185"/>
+      <c r="S49" s="185"/>
+      <c r="T49" s="185"/>
+      <c r="U49" s="185"/>
+      <c r="V49" s="186"/>
     </row>
     <row r="50" spans="1:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="114" t="s">
+      <c r="A50" s="196" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="115"/>
-      <c r="C50" s="115"/>
-      <c r="D50" s="115"/>
-      <c r="E50" s="115"/>
-      <c r="F50" s="115"/>
-      <c r="G50" s="115"/>
-      <c r="H50" s="115"/>
-      <c r="I50" s="115"/>
-      <c r="J50" s="115"/>
-      <c r="K50" s="115"/>
-      <c r="L50" s="115"/>
-      <c r="M50" s="115"/>
-      <c r="N50" s="115"/>
-      <c r="O50" s="115"/>
-      <c r="P50" s="115"/>
-      <c r="Q50" s="115"/>
-      <c r="R50" s="115"/>
-      <c r="S50" s="115"/>
-      <c r="T50" s="115"/>
-      <c r="U50" s="115"/>
-      <c r="V50" s="116"/>
+      <c r="B50" s="197"/>
+      <c r="C50" s="197"/>
+      <c r="D50" s="197"/>
+      <c r="E50" s="197"/>
+      <c r="F50" s="197"/>
+      <c r="G50" s="197"/>
+      <c r="H50" s="197"/>
+      <c r="I50" s="197"/>
+      <c r="J50" s="197"/>
+      <c r="K50" s="197"/>
+      <c r="L50" s="197"/>
+      <c r="M50" s="197"/>
+      <c r="N50" s="197"/>
+      <c r="O50" s="197"/>
+      <c r="P50" s="197"/>
+      <c r="Q50" s="197"/>
+      <c r="R50" s="197"/>
+      <c r="S50" s="197"/>
+      <c r="T50" s="197"/>
+      <c r="U50" s="197"/>
+      <c r="V50" s="198"/>
     </row>
     <row r="51" spans="1:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="105" t="s">
+      <c r="A51" s="187" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="106"/>
-      <c r="C51" s="106"/>
-      <c r="D51" s="106"/>
-      <c r="E51" s="106"/>
-      <c r="F51" s="106"/>
-      <c r="G51" s="106"/>
-      <c r="H51" s="106"/>
-      <c r="I51" s="106"/>
-      <c r="J51" s="106"/>
-      <c r="K51" s="106"/>
-      <c r="L51" s="106"/>
-      <c r="M51" s="106"/>
-      <c r="N51" s="106"/>
-      <c r="O51" s="106"/>
-      <c r="P51" s="106"/>
-      <c r="Q51" s="106"/>
-      <c r="R51" s="106"/>
-      <c r="S51" s="106"/>
-      <c r="T51" s="106"/>
-      <c r="U51" s="106"/>
-      <c r="V51" s="107"/>
+      <c r="B51" s="188"/>
+      <c r="C51" s="188"/>
+      <c r="D51" s="188"/>
+      <c r="E51" s="188"/>
+      <c r="F51" s="188"/>
+      <c r="G51" s="188"/>
+      <c r="H51" s="188"/>
+      <c r="I51" s="188"/>
+      <c r="J51" s="188"/>
+      <c r="K51" s="188"/>
+      <c r="L51" s="188"/>
+      <c r="M51" s="188"/>
+      <c r="N51" s="188"/>
+      <c r="O51" s="188"/>
+      <c r="P51" s="188"/>
+      <c r="Q51" s="188"/>
+      <c r="R51" s="188"/>
+      <c r="S51" s="188"/>
+      <c r="T51" s="188"/>
+      <c r="U51" s="188"/>
+      <c r="V51" s="189"/>
     </row>
     <row r="52" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="111" t="s">
+      <c r="A52" s="193" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="112"/>
-      <c r="C52" s="112"/>
-      <c r="D52" s="112"/>
-      <c r="E52" s="112"/>
-      <c r="F52" s="112"/>
-      <c r="G52" s="112"/>
-      <c r="H52" s="112"/>
-      <c r="I52" s="112"/>
-      <c r="J52" s="112"/>
-      <c r="K52" s="112"/>
-      <c r="L52" s="112"/>
-      <c r="M52" s="112"/>
-      <c r="N52" s="112"/>
-      <c r="O52" s="112"/>
-      <c r="P52" s="112"/>
-      <c r="Q52" s="112"/>
-      <c r="R52" s="112"/>
-      <c r="S52" s="112"/>
-      <c r="T52" s="112"/>
-      <c r="U52" s="112"/>
-      <c r="V52" s="113"/>
+      <c r="B52" s="194"/>
+      <c r="C52" s="194"/>
+      <c r="D52" s="194"/>
+      <c r="E52" s="194"/>
+      <c r="F52" s="194"/>
+      <c r="G52" s="194"/>
+      <c r="H52" s="194"/>
+      <c r="I52" s="194"/>
+      <c r="J52" s="194"/>
+      <c r="K52" s="194"/>
+      <c r="L52" s="194"/>
+      <c r="M52" s="194"/>
+      <c r="N52" s="194"/>
+      <c r="O52" s="194"/>
+      <c r="P52" s="194"/>
+      <c r="Q52" s="194"/>
+      <c r="R52" s="194"/>
+      <c r="S52" s="194"/>
+      <c r="T52" s="194"/>
+      <c r="U52" s="194"/>
+      <c r="V52" s="195"/>
     </row>
     <row r="53" spans="1:22" s="43" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="117" t="s">
+      <c r="A53" s="199" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="118"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
-      <c r="I53" s="118"/>
-      <c r="J53" s="118"/>
-      <c r="K53" s="118"/>
-      <c r="L53" s="118"/>
-      <c r="M53" s="118"/>
-      <c r="N53" s="118"/>
-      <c r="O53" s="118"/>
-      <c r="P53" s="118"/>
-      <c r="Q53" s="118"/>
-      <c r="R53" s="118"/>
-      <c r="S53" s="118"/>
-      <c r="T53" s="118"/>
-      <c r="U53" s="118"/>
-      <c r="V53" s="119"/>
+      <c r="B53" s="200"/>
+      <c r="C53" s="200"/>
+      <c r="D53" s="200"/>
+      <c r="E53" s="200"/>
+      <c r="F53" s="200"/>
+      <c r="G53" s="200"/>
+      <c r="H53" s="200"/>
+      <c r="I53" s="200"/>
+      <c r="J53" s="200"/>
+      <c r="K53" s="200"/>
+      <c r="L53" s="200"/>
+      <c r="M53" s="200"/>
+      <c r="N53" s="200"/>
+      <c r="O53" s="200"/>
+      <c r="P53" s="200"/>
+      <c r="Q53" s="200"/>
+      <c r="R53" s="200"/>
+      <c r="S53" s="200"/>
+      <c r="T53" s="200"/>
+      <c r="U53" s="200"/>
+      <c r="V53" s="201"/>
     </row>
     <row r="54" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="111" t="s">
+      <c r="A54" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="112"/>
-      <c r="C54" s="112"/>
-      <c r="D54" s="112"/>
-      <c r="E54" s="112"/>
-      <c r="F54" s="112"/>
-      <c r="G54" s="112"/>
-      <c r="H54" s="112"/>
-      <c r="I54" s="112"/>
-      <c r="J54" s="112"/>
-      <c r="K54" s="112"/>
-      <c r="L54" s="112"/>
-      <c r="M54" s="112"/>
-      <c r="N54" s="112"/>
-      <c r="O54" s="112"/>
-      <c r="P54" s="112"/>
-      <c r="Q54" s="112"/>
-      <c r="R54" s="112"/>
-      <c r="S54" s="112"/>
-      <c r="T54" s="112"/>
-      <c r="U54" s="112"/>
-      <c r="V54" s="113"/>
+      <c r="B54" s="194"/>
+      <c r="C54" s="194"/>
+      <c r="D54" s="194"/>
+      <c r="E54" s="194"/>
+      <c r="F54" s="194"/>
+      <c r="G54" s="194"/>
+      <c r="H54" s="194"/>
+      <c r="I54" s="194"/>
+      <c r="J54" s="194"/>
+      <c r="K54" s="194"/>
+      <c r="L54" s="194"/>
+      <c r="M54" s="194"/>
+      <c r="N54" s="194"/>
+      <c r="O54" s="194"/>
+      <c r="P54" s="194"/>
+      <c r="Q54" s="194"/>
+      <c r="R54" s="194"/>
+      <c r="S54" s="194"/>
+      <c r="T54" s="194"/>
+      <c r="U54" s="194"/>
+      <c r="V54" s="195"/>
     </row>
     <row r="55" spans="1:22" ht="247" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="108" t="s">
+      <c r="A55" s="190" t="s">
         <v>101</v>
       </c>
-      <c r="B55" s="109"/>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
-      <c r="F55" s="109"/>
-      <c r="G55" s="109"/>
-      <c r="H55" s="109"/>
-      <c r="I55" s="109"/>
-      <c r="J55" s="109"/>
-      <c r="K55" s="109"/>
-      <c r="L55" s="109"/>
-      <c r="M55" s="109"/>
-      <c r="N55" s="109"/>
-      <c r="O55" s="109"/>
-      <c r="P55" s="109"/>
-      <c r="Q55" s="109"/>
-      <c r="R55" s="109"/>
-      <c r="S55" s="109"/>
-      <c r="T55" s="109"/>
-      <c r="U55" s="109"/>
-      <c r="V55" s="110"/>
+      <c r="B55" s="191"/>
+      <c r="C55" s="191"/>
+      <c r="D55" s="191"/>
+      <c r="E55" s="191"/>
+      <c r="F55" s="191"/>
+      <c r="G55" s="191"/>
+      <c r="H55" s="191"/>
+      <c r="I55" s="191"/>
+      <c r="J55" s="191"/>
+      <c r="K55" s="191"/>
+      <c r="L55" s="191"/>
+      <c r="M55" s="191"/>
+      <c r="N55" s="191"/>
+      <c r="O55" s="191"/>
+      <c r="P55" s="191"/>
+      <c r="Q55" s="191"/>
+      <c r="R55" s="191"/>
+      <c r="S55" s="191"/>
+      <c r="T55" s="191"/>
+      <c r="U55" s="191"/>
+      <c r="V55" s="192"/>
     </row>
     <row r="56" spans="1:22" ht="9" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A56" s="44"/>
@@ -5128,30 +5122,30 @@
       <c r="V56" s="12"/>
     </row>
     <row r="57" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="62" t="s">
+      <c r="A57" s="214" t="s">
         <v>45</v>
       </c>
-      <c r="B57" s="62"/>
-      <c r="C57" s="62"/>
-      <c r="D57" s="62"/>
-      <c r="E57" s="62"/>
-      <c r="F57" s="62"/>
-      <c r="G57" s="62"/>
-      <c r="H57" s="62"/>
-      <c r="I57" s="62"/>
-      <c r="J57" s="62"/>
-      <c r="K57" s="62"/>
-      <c r="L57" s="62"/>
-      <c r="M57" s="62"/>
-      <c r="N57" s="62"/>
-      <c r="O57" s="62"/>
-      <c r="P57" s="62"/>
-      <c r="Q57" s="62"/>
-      <c r="R57" s="62"/>
-      <c r="S57" s="62"/>
-      <c r="T57" s="62"/>
-      <c r="U57" s="62"/>
-      <c r="V57" s="62"/>
+      <c r="B57" s="214"/>
+      <c r="C57" s="214"/>
+      <c r="D57" s="214"/>
+      <c r="E57" s="214"/>
+      <c r="F57" s="214"/>
+      <c r="G57" s="214"/>
+      <c r="H57" s="214"/>
+      <c r="I57" s="214"/>
+      <c r="J57" s="214"/>
+      <c r="K57" s="214"/>
+      <c r="L57" s="214"/>
+      <c r="M57" s="214"/>
+      <c r="N57" s="214"/>
+      <c r="O57" s="214"/>
+      <c r="P57" s="214"/>
+      <c r="Q57" s="214"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="214"/>
+      <c r="T57" s="214"/>
+      <c r="U57" s="214"/>
+      <c r="V57" s="214"/>
     </row>
     <row r="58" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="45"/>
@@ -5181,107 +5175,107 @@
       <c r="A59" s="46">
         <v>1</v>
       </c>
-      <c r="B59" s="63" t="s">
+      <c r="B59" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="63"/>
-      <c r="D59" s="63"/>
-      <c r="E59" s="63"/>
-      <c r="F59" s="63"/>
-      <c r="G59" s="63"/>
-      <c r="H59" s="63"/>
-      <c r="I59" s="63"/>
-      <c r="J59" s="63"/>
-      <c r="K59" s="63"/>
-      <c r="L59" s="63"/>
-      <c r="M59" s="63"/>
-      <c r="N59" s="63"/>
-      <c r="O59" s="63"/>
-      <c r="P59" s="63"/>
-      <c r="Q59" s="63"/>
-      <c r="R59" s="63"/>
-      <c r="S59" s="63"/>
-      <c r="T59" s="63"/>
-      <c r="U59" s="63"/>
-      <c r="V59" s="63"/>
+      <c r="C59" s="162"/>
+      <c r="D59" s="162"/>
+      <c r="E59" s="162"/>
+      <c r="F59" s="162"/>
+      <c r="G59" s="162"/>
+      <c r="H59" s="162"/>
+      <c r="I59" s="162"/>
+      <c r="J59" s="162"/>
+      <c r="K59" s="162"/>
+      <c r="L59" s="162"/>
+      <c r="M59" s="162"/>
+      <c r="N59" s="162"/>
+      <c r="O59" s="162"/>
+      <c r="P59" s="162"/>
+      <c r="Q59" s="162"/>
+      <c r="R59" s="162"/>
+      <c r="S59" s="162"/>
+      <c r="T59" s="162"/>
+      <c r="U59" s="162"/>
+      <c r="V59" s="162"/>
     </row>
     <row r="60" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="46"/>
-      <c r="B60" s="63" t="s">
+      <c r="B60" s="162" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="63"/>
-      <c r="D60" s="63"/>
-      <c r="E60" s="63"/>
-      <c r="F60" s="63"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="63"/>
-      <c r="I60" s="63"/>
-      <c r="J60" s="63"/>
-      <c r="K60" s="63"/>
-      <c r="L60" s="63"/>
-      <c r="M60" s="63"/>
-      <c r="N60" s="63"/>
-      <c r="O60" s="63"/>
-      <c r="P60" s="63"/>
-      <c r="Q60" s="63"/>
-      <c r="R60" s="63"/>
-      <c r="S60" s="63"/>
-      <c r="T60" s="63"/>
-      <c r="U60" s="63"/>
-      <c r="V60" s="63"/>
+      <c r="C60" s="162"/>
+      <c r="D60" s="162"/>
+      <c r="E60" s="162"/>
+      <c r="F60" s="162"/>
+      <c r="G60" s="162"/>
+      <c r="H60" s="162"/>
+      <c r="I60" s="162"/>
+      <c r="J60" s="162"/>
+      <c r="K60" s="162"/>
+      <c r="L60" s="162"/>
+      <c r="M60" s="162"/>
+      <c r="N60" s="162"/>
+      <c r="O60" s="162"/>
+      <c r="P60" s="162"/>
+      <c r="Q60" s="162"/>
+      <c r="R60" s="162"/>
+      <c r="S60" s="162"/>
+      <c r="T60" s="162"/>
+      <c r="U60" s="162"/>
+      <c r="V60" s="162"/>
     </row>
     <row r="61" spans="1:22" s="18" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="47"/>
-      <c r="B61" s="63" t="s">
+      <c r="B61" s="162" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="63"/>
-      <c r="D61" s="63"/>
-      <c r="E61" s="63"/>
-      <c r="F61" s="63"/>
-      <c r="G61" s="63"/>
-      <c r="H61" s="63"/>
-      <c r="I61" s="63"/>
-      <c r="J61" s="63"/>
-      <c r="K61" s="63"/>
-      <c r="L61" s="63"/>
-      <c r="M61" s="63"/>
-      <c r="N61" s="63"/>
-      <c r="O61" s="63"/>
-      <c r="P61" s="63"/>
-      <c r="Q61" s="63"/>
-      <c r="R61" s="63"/>
-      <c r="S61" s="63"/>
-      <c r="T61" s="63"/>
-      <c r="U61" s="63"/>
-      <c r="V61" s="63"/>
+      <c r="C61" s="162"/>
+      <c r="D61" s="162"/>
+      <c r="E61" s="162"/>
+      <c r="F61" s="162"/>
+      <c r="G61" s="162"/>
+      <c r="H61" s="162"/>
+      <c r="I61" s="162"/>
+      <c r="J61" s="162"/>
+      <c r="K61" s="162"/>
+      <c r="L61" s="162"/>
+      <c r="M61" s="162"/>
+      <c r="N61" s="162"/>
+      <c r="O61" s="162"/>
+      <c r="P61" s="162"/>
+      <c r="Q61" s="162"/>
+      <c r="R61" s="162"/>
+      <c r="S61" s="162"/>
+      <c r="T61" s="162"/>
+      <c r="U61" s="162"/>
+      <c r="V61" s="162"/>
     </row>
     <row r="62" spans="1:22" s="18" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="47"/>
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="162" t="s">
         <v>49</v>
       </c>
-      <c r="C62" s="63"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="63"/>
-      <c r="I62" s="63"/>
-      <c r="J62" s="63"/>
-      <c r="K62" s="63"/>
-      <c r="L62" s="63"/>
-      <c r="M62" s="63"/>
-      <c r="N62" s="63"/>
-      <c r="O62" s="63"/>
-      <c r="P62" s="63"/>
-      <c r="Q62" s="63"/>
-      <c r="R62" s="63"/>
-      <c r="S62" s="63"/>
-      <c r="T62" s="63"/>
-      <c r="U62" s="63"/>
-      <c r="V62" s="63"/>
+      <c r="C62" s="162"/>
+      <c r="D62" s="162"/>
+      <c r="E62" s="162"/>
+      <c r="F62" s="162"/>
+      <c r="G62" s="162"/>
+      <c r="H62" s="162"/>
+      <c r="I62" s="162"/>
+      <c r="J62" s="162"/>
+      <c r="K62" s="162"/>
+      <c r="L62" s="162"/>
+      <c r="M62" s="162"/>
+      <c r="N62" s="162"/>
+      <c r="O62" s="162"/>
+      <c r="P62" s="162"/>
+      <c r="Q62" s="162"/>
+      <c r="R62" s="162"/>
+      <c r="S62" s="162"/>
+      <c r="T62" s="162"/>
+      <c r="U62" s="162"/>
+      <c r="V62" s="162"/>
     </row>
     <row r="63" spans="1:22" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A63" s="18" t="s">
@@ -5306,105 +5300,105 @@
       <c r="A64" s="38">
         <v>2</v>
       </c>
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="162" t="s">
         <v>51</v>
       </c>
-      <c r="C64" s="63"/>
-      <c r="D64" s="63"/>
-      <c r="E64" s="63"/>
-      <c r="F64" s="63"/>
-      <c r="G64" s="63"/>
-      <c r="H64" s="63"/>
-      <c r="I64" s="63"/>
-      <c r="J64" s="63"/>
-      <c r="K64" s="63"/>
-      <c r="L64" s="63"/>
-      <c r="M64" s="63"/>
-      <c r="N64" s="63"/>
-      <c r="O64" s="63"/>
-      <c r="P64" s="63"/>
-      <c r="Q64" s="63"/>
-      <c r="R64" s="63"/>
-      <c r="S64" s="63"/>
-      <c r="T64" s="63"/>
-      <c r="U64" s="63"/>
-      <c r="V64" s="63"/>
+      <c r="C64" s="162"/>
+      <c r="D64" s="162"/>
+      <c r="E64" s="162"/>
+      <c r="F64" s="162"/>
+      <c r="G64" s="162"/>
+      <c r="H64" s="162"/>
+      <c r="I64" s="162"/>
+      <c r="J64" s="162"/>
+      <c r="K64" s="162"/>
+      <c r="L64" s="162"/>
+      <c r="M64" s="162"/>
+      <c r="N64" s="162"/>
+      <c r="O64" s="162"/>
+      <c r="P64" s="162"/>
+      <c r="Q64" s="162"/>
+      <c r="R64" s="162"/>
+      <c r="S64" s="162"/>
+      <c r="T64" s="162"/>
+      <c r="U64" s="162"/>
+      <c r="V64" s="162"/>
     </row>
     <row r="65" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="38"/>
-      <c r="B65" s="63" t="s">
+      <c r="B65" s="162" t="s">
         <v>52</v>
       </c>
-      <c r="C65" s="63"/>
-      <c r="D65" s="63"/>
-      <c r="E65" s="63"/>
-      <c r="F65" s="63"/>
-      <c r="G65" s="63"/>
-      <c r="H65" s="63"/>
-      <c r="I65" s="63"/>
-      <c r="J65" s="63"/>
-      <c r="K65" s="63"/>
-      <c r="L65" s="63"/>
-      <c r="M65" s="63"/>
-      <c r="N65" s="63"/>
-      <c r="O65" s="63"/>
-      <c r="P65" s="63"/>
-      <c r="Q65" s="63"/>
-      <c r="R65" s="63"/>
-      <c r="S65" s="63"/>
-      <c r="T65" s="63"/>
-      <c r="U65" s="63"/>
-      <c r="V65" s="63"/>
+      <c r="C65" s="162"/>
+      <c r="D65" s="162"/>
+      <c r="E65" s="162"/>
+      <c r="F65" s="162"/>
+      <c r="G65" s="162"/>
+      <c r="H65" s="162"/>
+      <c r="I65" s="162"/>
+      <c r="J65" s="162"/>
+      <c r="K65" s="162"/>
+      <c r="L65" s="162"/>
+      <c r="M65" s="162"/>
+      <c r="N65" s="162"/>
+      <c r="O65" s="162"/>
+      <c r="P65" s="162"/>
+      <c r="Q65" s="162"/>
+      <c r="R65" s="162"/>
+      <c r="S65" s="162"/>
+      <c r="T65" s="162"/>
+      <c r="U65" s="162"/>
+      <c r="V65" s="162"/>
     </row>
     <row r="66" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="64"/>
-      <c r="B66" s="64"/>
-      <c r="C66" s="64"/>
-      <c r="D66" s="64"/>
-      <c r="E66" s="64"/>
-      <c r="F66" s="64"/>
-      <c r="G66" s="64"/>
-      <c r="H66" s="64"/>
-      <c r="I66" s="64"/>
-      <c r="J66" s="64"/>
-      <c r="K66" s="64"/>
-      <c r="L66" s="64"/>
-      <c r="M66" s="64"/>
-      <c r="N66" s="64"/>
-      <c r="O66" s="64"/>
-      <c r="P66" s="64"/>
-      <c r="Q66" s="64"/>
-      <c r="R66" s="64"/>
-      <c r="S66" s="64"/>
-      <c r="T66" s="64"/>
-      <c r="U66" s="64"/>
-      <c r="V66" s="64"/>
+      <c r="A66" s="215"/>
+      <c r="B66" s="215"/>
+      <c r="C66" s="215"/>
+      <c r="D66" s="215"/>
+      <c r="E66" s="215"/>
+      <c r="F66" s="215"/>
+      <c r="G66" s="215"/>
+      <c r="H66" s="215"/>
+      <c r="I66" s="215"/>
+      <c r="J66" s="215"/>
+      <c r="K66" s="215"/>
+      <c r="L66" s="215"/>
+      <c r="M66" s="215"/>
+      <c r="N66" s="215"/>
+      <c r="O66" s="215"/>
+      <c r="P66" s="215"/>
+      <c r="Q66" s="215"/>
+      <c r="R66" s="215"/>
+      <c r="S66" s="215"/>
+      <c r="T66" s="215"/>
+      <c r="U66" s="215"/>
+      <c r="V66" s="215"/>
     </row>
     <row r="67" spans="1:22" ht="19" x14ac:dyDescent="0.2">
-      <c r="A67" s="63" t="s">
+      <c r="A67" s="162" t="s">
         <v>53</v>
       </c>
-      <c r="B67" s="63"/>
-      <c r="C67" s="63"/>
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="63"/>
-      <c r="G67" s="63"/>
-      <c r="H67" s="63"/>
-      <c r="I67" s="63"/>
-      <c r="J67" s="63"/>
-      <c r="K67" s="63"/>
-      <c r="L67" s="63"/>
-      <c r="M67" s="63"/>
-      <c r="N67" s="63"/>
-      <c r="O67" s="63"/>
-      <c r="P67" s="63"/>
-      <c r="Q67" s="63"/>
-      <c r="R67" s="63"/>
-      <c r="S67" s="63"/>
-      <c r="T67" s="63"/>
-      <c r="U67" s="63"/>
-      <c r="V67" s="63"/>
+      <c r="B67" s="162"/>
+      <c r="C67" s="162"/>
+      <c r="D67" s="162"/>
+      <c r="E67" s="162"/>
+      <c r="F67" s="162"/>
+      <c r="G67" s="162"/>
+      <c r="H67" s="162"/>
+      <c r="I67" s="162"/>
+      <c r="J67" s="162"/>
+      <c r="K67" s="162"/>
+      <c r="L67" s="162"/>
+      <c r="M67" s="162"/>
+      <c r="N67" s="162"/>
+      <c r="O67" s="162"/>
+      <c r="P67" s="162"/>
+      <c r="Q67" s="162"/>
+      <c r="R67" s="162"/>
+      <c r="S67" s="162"/>
+      <c r="T67" s="162"/>
+      <c r="U67" s="162"/>
+      <c r="V67" s="162"/>
     </row>
     <row r="68" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="69" spans="1:22" ht="21" x14ac:dyDescent="0.2">
@@ -5415,24 +5409,24 @@
       <c r="I69" s="20"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18"/>
-      <c r="L69" s="65" t="s">
+      <c r="L69" s="216" t="s">
         <v>86</v>
       </c>
-      <c r="M69" s="65"/>
+      <c r="M69" s="216"/>
       <c r="N69" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="O69" s="65" t="s">
+      <c r="O69" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="P69" s="65"/>
+      <c r="P69" s="216"/>
       <c r="Q69" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="R69" s="65" t="s">
+      <c r="R69" s="216" t="s">
         <v>88</v>
       </c>
-      <c r="S69" s="65"/>
+      <c r="S69" s="216"/>
       <c r="T69" s="18" t="s">
         <v>57</v>
       </c>
@@ -5466,56 +5460,56 @@
       <c r="V71" s="12"/>
     </row>
     <row r="72" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="62" t="s">
+      <c r="A72" s="214" t="s">
         <v>58</v>
       </c>
-      <c r="B72" s="62"/>
-      <c r="C72" s="62"/>
-      <c r="D72" s="62"/>
-      <c r="E72" s="62"/>
-      <c r="F72" s="62"/>
-      <c r="G72" s="62"/>
-      <c r="H72" s="62"/>
-      <c r="I72" s="62"/>
-      <c r="J72" s="62"/>
-      <c r="K72" s="62"/>
-      <c r="L72" s="62"/>
-      <c r="M72" s="62"/>
-      <c r="N72" s="62"/>
-      <c r="O72" s="62"/>
-      <c r="P72" s="62"/>
-      <c r="Q72" s="62"/>
-      <c r="R72" s="62"/>
-      <c r="S72" s="62"/>
-      <c r="T72" s="62"/>
-      <c r="U72" s="62"/>
-      <c r="V72" s="62"/>
+      <c r="B72" s="214"/>
+      <c r="C72" s="214"/>
+      <c r="D72" s="214"/>
+      <c r="E72" s="214"/>
+      <c r="F72" s="214"/>
+      <c r="G72" s="214"/>
+      <c r="H72" s="214"/>
+      <c r="I72" s="214"/>
+      <c r="J72" s="214"/>
+      <c r="K72" s="214"/>
+      <c r="L72" s="214"/>
+      <c r="M72" s="214"/>
+      <c r="N72" s="214"/>
+      <c r="O72" s="214"/>
+      <c r="P72" s="214"/>
+      <c r="Q72" s="214"/>
+      <c r="R72" s="214"/>
+      <c r="S72" s="214"/>
+      <c r="T72" s="214"/>
+      <c r="U72" s="214"/>
+      <c r="V72" s="214"/>
     </row>
     <row r="73" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="60" t="s">
+      <c r="A73" s="151" t="s">
         <v>59</v>
       </c>
-      <c r="B73" s="60"/>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="60"/>
-      <c r="F73" s="60"/>
-      <c r="G73" s="60"/>
-      <c r="H73" s="60"/>
-      <c r="I73" s="60"/>
-      <c r="J73" s="60"/>
-      <c r="K73" s="60"/>
-      <c r="L73" s="60"/>
-      <c r="M73" s="60"/>
-      <c r="N73" s="60"/>
-      <c r="O73" s="60"/>
-      <c r="P73" s="60"/>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="60"/>
-      <c r="S73" s="60"/>
-      <c r="T73" s="60"/>
-      <c r="U73" s="60"/>
-      <c r="V73" s="60"/>
+      <c r="B73" s="151"/>
+      <c r="C73" s="151"/>
+      <c r="D73" s="151"/>
+      <c r="E73" s="151"/>
+      <c r="F73" s="151"/>
+      <c r="G73" s="151"/>
+      <c r="H73" s="151"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="151"/>
+      <c r="K73" s="151"/>
+      <c r="L73" s="151"/>
+      <c r="M73" s="151"/>
+      <c r="N73" s="151"/>
+      <c r="O73" s="151"/>
+      <c r="P73" s="151"/>
+      <c r="Q73" s="151"/>
+      <c r="R73" s="151"/>
+      <c r="S73" s="151"/>
+      <c r="T73" s="151"/>
+      <c r="U73" s="151"/>
+      <c r="V73" s="151"/>
     </row>
     <row r="74" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" s="20"/>
@@ -5523,43 +5517,43 @@
       <c r="I74" s="20"/>
       <c r="J74" s="18"/>
       <c r="K74" s="18"/>
-      <c r="L74" s="61"/>
-      <c r="M74" s="61"/>
+      <c r="L74" s="213"/>
+      <c r="M74" s="213"/>
       <c r="N74" s="38"/>
-      <c r="O74" s="61"/>
-      <c r="P74" s="61"/>
+      <c r="O74" s="213"/>
+      <c r="P74" s="213"/>
       <c r="Q74" s="41"/>
-      <c r="R74" s="61"/>
-      <c r="S74" s="61"/>
+      <c r="R74" s="213"/>
+      <c r="S74" s="213"/>
       <c r="T74" s="18"/>
       <c r="U74" s="18"/>
       <c r="V74" s="20"/>
     </row>
     <row r="75" spans="1:22" s="18" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="60" t="s">
+      <c r="A75" s="151" t="s">
         <v>60</v>
       </c>
-      <c r="B75" s="60"/>
-      <c r="C75" s="60"/>
-      <c r="D75" s="60"/>
-      <c r="E75" s="60"/>
-      <c r="F75" s="60"/>
-      <c r="G75" s="60"/>
-      <c r="H75" s="60"/>
-      <c r="I75" s="60"/>
-      <c r="J75" s="60"/>
-      <c r="K75" s="60"/>
-      <c r="L75" s="60"/>
-      <c r="M75" s="60"/>
-      <c r="N75" s="60"/>
-      <c r="O75" s="60"/>
-      <c r="P75" s="60"/>
-      <c r="Q75" s="60"/>
-      <c r="R75" s="60"/>
-      <c r="S75" s="60"/>
-      <c r="T75" s="60"/>
-      <c r="U75" s="60"/>
-      <c r="V75" s="60"/>
+      <c r="B75" s="151"/>
+      <c r="C75" s="151"/>
+      <c r="D75" s="151"/>
+      <c r="E75" s="151"/>
+      <c r="F75" s="151"/>
+      <c r="G75" s="151"/>
+      <c r="H75" s="151"/>
+      <c r="I75" s="151"/>
+      <c r="J75" s="151"/>
+      <c r="K75" s="151"/>
+      <c r="L75" s="151"/>
+      <c r="M75" s="151"/>
+      <c r="N75" s="151"/>
+      <c r="O75" s="151"/>
+      <c r="P75" s="151"/>
+      <c r="Q75" s="151"/>
+      <c r="R75" s="151"/>
+      <c r="S75" s="151"/>
+      <c r="T75" s="151"/>
+      <c r="U75" s="151"/>
+      <c r="V75" s="151"/>
     </row>
     <row r="76" spans="1:22" s="18" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K76" s="41"/>
@@ -5567,39 +5561,27 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7tyF5rAkVSSKon2VuwXAnpy+jB/3rEKc+w3koIlqSKBK1t6Uk6bpumw0Ga6EHBIlPY/ZKS0rjQu6JCQhhsgcBA==" saltValue="FKvil65sGIO+xhVKxJNvsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="70">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="N4:V4"/>
-    <mergeCell ref="A5:D9"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:J9"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:U6"/>
-    <mergeCell ref="O7:U8"/>
-    <mergeCell ref="M7:N8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="A16:D20"/>
-    <mergeCell ref="E16:V20"/>
-    <mergeCell ref="A21:D25"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I21:V21"/>
-    <mergeCell ref="E22:V25"/>
-    <mergeCell ref="A10:D15"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:Q10"/>
-    <mergeCell ref="R10:S15"/>
-    <mergeCell ref="T10:U15"/>
-    <mergeCell ref="E11:Q15"/>
-    <mergeCell ref="A26:D31"/>
-    <mergeCell ref="E26:F28"/>
-    <mergeCell ref="G26:R28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="E29:F31"/>
-    <mergeCell ref="G29:R31"/>
-    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="A75:V75"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="O74:P74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="A57:V57"/>
+    <mergeCell ref="B59:V59"/>
+    <mergeCell ref="B61:V61"/>
+    <mergeCell ref="B62:V62"/>
+    <mergeCell ref="A73:V73"/>
+    <mergeCell ref="B65:V65"/>
+    <mergeCell ref="A66:V66"/>
+    <mergeCell ref="A67:V67"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="O69:P69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="A72:V72"/>
+    <mergeCell ref="H38:V38"/>
+    <mergeCell ref="E39:V40"/>
+    <mergeCell ref="C43:U43"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:V47"/>
     <mergeCell ref="B64:V64"/>
     <mergeCell ref="A33:D37"/>
     <mergeCell ref="F33:V33"/>
@@ -5616,27 +5598,39 @@
     <mergeCell ref="A52:V52"/>
     <mergeCell ref="A53:V53"/>
     <mergeCell ref="A38:D40"/>
-    <mergeCell ref="H38:V38"/>
-    <mergeCell ref="E39:V40"/>
-    <mergeCell ref="C43:U43"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:V47"/>
-    <mergeCell ref="A75:V75"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="O74:P74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="A57:V57"/>
-    <mergeCell ref="B59:V59"/>
-    <mergeCell ref="B61:V61"/>
-    <mergeCell ref="B62:V62"/>
-    <mergeCell ref="A73:V73"/>
-    <mergeCell ref="B65:V65"/>
-    <mergeCell ref="A66:V66"/>
-    <mergeCell ref="A67:V67"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="O69:P69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="A72:V72"/>
+    <mergeCell ref="A26:D31"/>
+    <mergeCell ref="E26:F28"/>
+    <mergeCell ref="G26:R28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="E29:F31"/>
+    <mergeCell ref="G29:R31"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="A16:D20"/>
+    <mergeCell ref="E16:V20"/>
+    <mergeCell ref="A21:D25"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="I21:V21"/>
+    <mergeCell ref="E22:V25"/>
+    <mergeCell ref="A10:D15"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:Q10"/>
+    <mergeCell ref="R10:S15"/>
+    <mergeCell ref="T10:U15"/>
+    <mergeCell ref="E11:Q15"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="A5:D9"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:J9"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="O7:U8"/>
+    <mergeCell ref="M7:N8"/>
+    <mergeCell ref="M9:U9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -5778,18 +5772,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="187"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:22" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5806,17 +5800,17 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
-      <c r="M2" s="188" t="s">
+      <c r="M2" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="N2" s="189"/>
-      <c r="O2" s="189"/>
-      <c r="P2" s="189"/>
-      <c r="Q2" s="190"/>
-      <c r="S2" s="191"/>
-      <c r="T2" s="192"/>
-      <c r="U2" s="192"/>
-      <c r="V2" s="193"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="63"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="66"/>
     </row>
     <row r="3" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
@@ -5841,1849 +5835,1917 @@
       <c r="V3" s="11"/>
     </row>
     <row r="4" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="N4" s="194" t="s">
+      <c r="N4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="194"/>
-      <c r="P4" s="194"/>
-      <c r="Q4" s="194"/>
-      <c r="R4" s="194"/>
-      <c r="S4" s="194"/>
-      <c r="T4" s="194"/>
-      <c r="U4" s="194"/>
-      <c r="V4" s="194"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="195" t="s">
+      <c r="A5" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="225" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="226"/>
-      <c r="G5" s="227"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="227"/>
-      <c r="K5" s="227"/>
-      <c r="L5" s="227"/>
-      <c r="M5" s="227"/>
-      <c r="N5" s="227"/>
-      <c r="O5" s="227"/>
-      <c r="P5" s="227"/>
-      <c r="Q5" s="227"/>
-      <c r="R5" s="227"/>
-      <c r="S5" s="227"/>
-      <c r="T5" s="227"/>
-      <c r="U5" s="227"/>
-      <c r="V5" s="250"/>
+      <c r="F5" s="218"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="219"/>
+      <c r="K5" s="219"/>
+      <c r="L5" s="219"/>
+      <c r="M5" s="219"/>
+      <c r="N5" s="219"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="219"/>
+      <c r="Q5" s="219"/>
+      <c r="R5" s="219"/>
+      <c r="S5" s="219"/>
+      <c r="T5" s="219"/>
+      <c r="U5" s="219"/>
+      <c r="V5" s="220"/>
     </row>
     <row r="6" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="198"/>
-      <c r="B6" s="199"/>
-      <c r="C6" s="199"/>
-      <c r="D6" s="200"/>
-      <c r="E6" s="243"/>
-      <c r="F6" s="244"/>
-      <c r="G6" s="244"/>
-      <c r="H6" s="244"/>
-      <c r="I6" s="244"/>
-      <c r="J6" s="244"/>
-      <c r="K6" s="244"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="244"/>
-      <c r="N6" s="244"/>
-      <c r="O6" s="244"/>
-      <c r="P6" s="244"/>
-      <c r="Q6" s="244"/>
-      <c r="R6" s="244"/>
-      <c r="S6" s="244"/>
-      <c r="T6" s="244"/>
-      <c r="U6" s="244"/>
-      <c r="V6" s="251"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="221"/>
+      <c r="F6" s="222"/>
+      <c r="G6" s="222"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="222"/>
+      <c r="J6" s="222"/>
+      <c r="K6" s="222"/>
+      <c r="L6" s="222"/>
+      <c r="M6" s="222"/>
+      <c r="N6" s="222"/>
+      <c r="O6" s="222"/>
+      <c r="P6" s="222"/>
+      <c r="Q6" s="222"/>
+      <c r="R6" s="222"/>
+      <c r="S6" s="222"/>
+      <c r="T6" s="222"/>
+      <c r="U6" s="222"/>
+      <c r="V6" s="223"/>
     </row>
     <row r="7" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="198"/>
-      <c r="B7" s="199"/>
-      <c r="C7" s="199"/>
-      <c r="D7" s="200"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="253"/>
-      <c r="G7" s="253"/>
-      <c r="H7" s="253"/>
-      <c r="I7" s="253"/>
-      <c r="J7" s="253"/>
-      <c r="K7" s="253"/>
-      <c r="L7" s="253"/>
-      <c r="M7" s="253"/>
-      <c r="N7" s="253"/>
-      <c r="O7" s="253"/>
-      <c r="P7" s="253"/>
-      <c r="Q7" s="253"/>
-      <c r="R7" s="253"/>
-      <c r="S7" s="253"/>
-      <c r="T7" s="253"/>
-      <c r="U7" s="253"/>
-      <c r="V7" s="254"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="225"/>
+      <c r="G7" s="225"/>
+      <c r="H7" s="225"/>
+      <c r="I7" s="225"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
+      <c r="M7" s="225"/>
+      <c r="N7" s="225"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="225"/>
+      <c r="Q7" s="225"/>
+      <c r="R7" s="225"/>
+      <c r="S7" s="225"/>
+      <c r="T7" s="225"/>
+      <c r="U7" s="225"/>
+      <c r="V7" s="226"/>
     </row>
     <row r="8" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="198"/>
-      <c r="B8" s="199"/>
-      <c r="C8" s="199"/>
-      <c r="D8" s="200"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253"/>
-      <c r="H8" s="253"/>
-      <c r="I8" s="253"/>
-      <c r="J8" s="253"/>
-      <c r="K8" s="253"/>
-      <c r="L8" s="253"/>
-      <c r="M8" s="253"/>
-      <c r="N8" s="253"/>
-      <c r="O8" s="253"/>
-      <c r="P8" s="253"/>
-      <c r="Q8" s="253"/>
-      <c r="R8" s="253"/>
-      <c r="S8" s="253"/>
-      <c r="T8" s="253"/>
-      <c r="U8" s="253"/>
-      <c r="V8" s="254"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="225"/>
+      <c r="G8" s="225"/>
+      <c r="H8" s="225"/>
+      <c r="I8" s="225"/>
+      <c r="J8" s="225"/>
+      <c r="K8" s="225"/>
+      <c r="L8" s="225"/>
+      <c r="M8" s="225"/>
+      <c r="N8" s="225"/>
+      <c r="O8" s="225"/>
+      <c r="P8" s="225"/>
+      <c r="Q8" s="225"/>
+      <c r="R8" s="225"/>
+      <c r="S8" s="225"/>
+      <c r="T8" s="225"/>
+      <c r="U8" s="225"/>
+      <c r="V8" s="226"/>
     </row>
     <row r="9" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="201"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="247"/>
-      <c r="G9" s="247"/>
-      <c r="H9" s="247"/>
-      <c r="I9" s="247"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="247"/>
-      <c r="M9" s="247"/>
-      <c r="N9" s="247"/>
-      <c r="O9" s="247"/>
-      <c r="P9" s="247"/>
-      <c r="Q9" s="247"/>
-      <c r="R9" s="247"/>
-      <c r="S9" s="247"/>
-      <c r="T9" s="247"/>
-      <c r="U9" s="247"/>
-      <c r="V9" s="255"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="228"/>
+      <c r="G9" s="228"/>
+      <c r="H9" s="228"/>
+      <c r="I9" s="228"/>
+      <c r="J9" s="228"/>
+      <c r="K9" s="228"/>
+      <c r="L9" s="228"/>
+      <c r="M9" s="228"/>
+      <c r="N9" s="228"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="228"/>
+      <c r="Q9" s="228"/>
+      <c r="R9" s="228"/>
+      <c r="S9" s="228"/>
+      <c r="T9" s="228"/>
+      <c r="U9" s="228"/>
+      <c r="V9" s="229"/>
     </row>
     <row r="10" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="195" t="s">
+      <c r="A10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="196"/>
-      <c r="C10" s="196"/>
-      <c r="D10" s="197"/>
-      <c r="E10" s="225" t="s">
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="226"/>
-      <c r="G10" s="227"/>
-      <c r="H10" s="227"/>
-      <c r="I10" s="227"/>
-      <c r="J10" s="227"/>
-      <c r="K10" s="227"/>
-      <c r="L10" s="227"/>
-      <c r="M10" s="227"/>
-      <c r="N10" s="227"/>
-      <c r="O10" s="227"/>
-      <c r="P10" s="227"/>
-      <c r="Q10" s="227"/>
-      <c r="R10" s="227"/>
-      <c r="S10" s="227"/>
-      <c r="T10" s="227"/>
-      <c r="U10" s="227"/>
-      <c r="V10" s="250"/>
+      <c r="F10" s="218"/>
+      <c r="G10" s="219"/>
+      <c r="H10" s="219"/>
+      <c r="I10" s="219"/>
+      <c r="J10" s="219"/>
+      <c r="K10" s="219"/>
+      <c r="L10" s="219"/>
+      <c r="M10" s="219"/>
+      <c r="N10" s="219"/>
+      <c r="O10" s="219"/>
+      <c r="P10" s="219"/>
+      <c r="Q10" s="219"/>
+      <c r="R10" s="219"/>
+      <c r="S10" s="219"/>
+      <c r="T10" s="219"/>
+      <c r="U10" s="219"/>
+      <c r="V10" s="220"/>
     </row>
     <row r="11" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="198"/>
-      <c r="B11" s="199"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="200"/>
-      <c r="E11" s="243"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
-      <c r="M11" s="244"/>
-      <c r="N11" s="244"/>
-      <c r="O11" s="244"/>
-      <c r="P11" s="244"/>
-      <c r="Q11" s="244"/>
-      <c r="R11" s="244"/>
-      <c r="S11" s="244"/>
-      <c r="T11" s="244"/>
-      <c r="U11" s="244"/>
-      <c r="V11" s="251"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="222"/>
+      <c r="G11" s="222"/>
+      <c r="H11" s="222"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="222"/>
+      <c r="K11" s="222"/>
+      <c r="L11" s="222"/>
+      <c r="M11" s="222"/>
+      <c r="N11" s="222"/>
+      <c r="O11" s="222"/>
+      <c r="P11" s="222"/>
+      <c r="Q11" s="222"/>
+      <c r="R11" s="222"/>
+      <c r="S11" s="222"/>
+      <c r="T11" s="222"/>
+      <c r="U11" s="222"/>
+      <c r="V11" s="223"/>
     </row>
     <row r="12" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="198"/>
-      <c r="B12" s="199"/>
-      <c r="C12" s="199"/>
-      <c r="D12" s="200"/>
-      <c r="E12" s="252"/>
-      <c r="F12" s="253"/>
-      <c r="G12" s="253"/>
-      <c r="H12" s="253"/>
-      <c r="I12" s="253"/>
-      <c r="J12" s="253"/>
-      <c r="K12" s="253"/>
-      <c r="L12" s="253"/>
-      <c r="M12" s="253"/>
-      <c r="N12" s="253"/>
-      <c r="O12" s="253"/>
-      <c r="P12" s="253"/>
-      <c r="Q12" s="253"/>
-      <c r="R12" s="253"/>
-      <c r="S12" s="253"/>
-      <c r="T12" s="253"/>
-      <c r="U12" s="253"/>
-      <c r="V12" s="254"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="224"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
+      <c r="M12" s="225"/>
+      <c r="N12" s="225"/>
+      <c r="O12" s="225"/>
+      <c r="P12" s="225"/>
+      <c r="Q12" s="225"/>
+      <c r="R12" s="225"/>
+      <c r="S12" s="225"/>
+      <c r="T12" s="225"/>
+      <c r="U12" s="225"/>
+      <c r="V12" s="226"/>
     </row>
     <row r="13" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="198"/>
-      <c r="B13" s="199"/>
-      <c r="C13" s="199"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="253"/>
-      <c r="G13" s="253"/>
-      <c r="H13" s="253"/>
-      <c r="I13" s="253"/>
-      <c r="J13" s="253"/>
-      <c r="K13" s="253"/>
-      <c r="L13" s="253"/>
-      <c r="M13" s="253"/>
-      <c r="N13" s="253"/>
-      <c r="O13" s="253"/>
-      <c r="P13" s="253"/>
-      <c r="Q13" s="253"/>
-      <c r="R13" s="253"/>
-      <c r="S13" s="253"/>
-      <c r="T13" s="253"/>
-      <c r="U13" s="253"/>
-      <c r="V13" s="254"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="224"/>
+      <c r="F13" s="225"/>
+      <c r="G13" s="225"/>
+      <c r="H13" s="225"/>
+      <c r="I13" s="225"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="225"/>
+      <c r="M13" s="225"/>
+      <c r="N13" s="225"/>
+      <c r="O13" s="225"/>
+      <c r="P13" s="225"/>
+      <c r="Q13" s="225"/>
+      <c r="R13" s="225"/>
+      <c r="S13" s="225"/>
+      <c r="T13" s="225"/>
+      <c r="U13" s="225"/>
+      <c r="V13" s="226"/>
     </row>
     <row r="14" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="201"/>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="246"/>
-      <c r="F14" s="247"/>
-      <c r="G14" s="247"/>
-      <c r="H14" s="247"/>
-      <c r="I14" s="247"/>
-      <c r="J14" s="247"/>
-      <c r="K14" s="247"/>
-      <c r="L14" s="247"/>
-      <c r="M14" s="247"/>
-      <c r="N14" s="247"/>
-      <c r="O14" s="247"/>
-      <c r="P14" s="247"/>
-      <c r="Q14" s="247"/>
-      <c r="R14" s="247"/>
-      <c r="S14" s="247"/>
-      <c r="T14" s="247"/>
-      <c r="U14" s="247"/>
-      <c r="V14" s="255"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="227"/>
+      <c r="F14" s="228"/>
+      <c r="G14" s="228"/>
+      <c r="H14" s="228"/>
+      <c r="I14" s="228"/>
+      <c r="J14" s="228"/>
+      <c r="K14" s="228"/>
+      <c r="L14" s="228"/>
+      <c r="M14" s="228"/>
+      <c r="N14" s="228"/>
+      <c r="O14" s="228"/>
+      <c r="P14" s="228"/>
+      <c r="Q14" s="228"/>
+      <c r="R14" s="228"/>
+      <c r="S14" s="228"/>
+      <c r="T14" s="228"/>
+      <c r="U14" s="228"/>
+      <c r="V14" s="229"/>
     </row>
     <row r="15" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="195" t="s">
+      <c r="A15" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="196"/>
-      <c r="C15" s="196"/>
-      <c r="D15" s="197"/>
-      <c r="E15" s="225" t="s">
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="226"/>
-      <c r="G15" s="227"/>
-      <c r="H15" s="227"/>
-      <c r="I15" s="227"/>
-      <c r="J15" s="227"/>
-      <c r="K15" s="227"/>
-      <c r="L15" s="227"/>
-      <c r="M15" s="228"/>
-      <c r="N15" s="229" t="s">
+      <c r="F15" s="218"/>
+      <c r="G15" s="219"/>
+      <c r="H15" s="219"/>
+      <c r="I15" s="219"/>
+      <c r="J15" s="219"/>
+      <c r="K15" s="219"/>
+      <c r="L15" s="219"/>
+      <c r="M15" s="230"/>
+      <c r="N15" s="231" t="s">
         <v>65</v>
       </c>
-      <c r="O15" s="217"/>
-      <c r="P15" s="217"/>
-      <c r="Q15" s="218"/>
-      <c r="R15" s="234"/>
-      <c r="S15" s="235"/>
-      <c r="T15" s="235"/>
-      <c r="U15" s="235"/>
-      <c r="V15" s="236"/>
+      <c r="O15" s="232"/>
+      <c r="P15" s="232"/>
+      <c r="Q15" s="233"/>
+      <c r="R15" s="240"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="241"/>
+      <c r="U15" s="241"/>
+      <c r="V15" s="242"/>
     </row>
     <row r="16" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="198"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="199"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="243"/>
-      <c r="F16" s="244"/>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="244"/>
-      <c r="K16" s="244"/>
-      <c r="L16" s="244"/>
-      <c r="M16" s="245"/>
-      <c r="N16" s="230"/>
-      <c r="O16" s="220"/>
-      <c r="P16" s="220"/>
-      <c r="Q16" s="221"/>
-      <c r="R16" s="237"/>
-      <c r="S16" s="238"/>
-      <c r="T16" s="238"/>
-      <c r="U16" s="238"/>
-      <c r="V16" s="239"/>
+      <c r="A16" s="71"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="221"/>
+      <c r="F16" s="222"/>
+      <c r="G16" s="222"/>
+      <c r="H16" s="222"/>
+      <c r="I16" s="222"/>
+      <c r="J16" s="222"/>
+      <c r="K16" s="222"/>
+      <c r="L16" s="222"/>
+      <c r="M16" s="249"/>
+      <c r="N16" s="234"/>
+      <c r="O16" s="235"/>
+      <c r="P16" s="235"/>
+      <c r="Q16" s="236"/>
+      <c r="R16" s="243"/>
+      <c r="S16" s="244"/>
+      <c r="T16" s="244"/>
+      <c r="U16" s="244"/>
+      <c r="V16" s="245"/>
     </row>
     <row r="17" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="201"/>
-      <c r="B17" s="202"/>
-      <c r="C17" s="202"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
-      <c r="J17" s="247"/>
-      <c r="K17" s="247"/>
-      <c r="L17" s="247"/>
-      <c r="M17" s="248"/>
-      <c r="N17" s="231"/>
-      <c r="O17" s="232"/>
-      <c r="P17" s="232"/>
-      <c r="Q17" s="233"/>
-      <c r="R17" s="240"/>
-      <c r="S17" s="241"/>
-      <c r="T17" s="241"/>
-      <c r="U17" s="241"/>
-      <c r="V17" s="242"/>
+      <c r="A17" s="74"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="227"/>
+      <c r="F17" s="228"/>
+      <c r="G17" s="228"/>
+      <c r="H17" s="228"/>
+      <c r="I17" s="228"/>
+      <c r="J17" s="228"/>
+      <c r="K17" s="228"/>
+      <c r="L17" s="228"/>
+      <c r="M17" s="250"/>
+      <c r="N17" s="237"/>
+      <c r="O17" s="238"/>
+      <c r="P17" s="238"/>
+      <c r="Q17" s="239"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="247"/>
+      <c r="T17" s="247"/>
+      <c r="U17" s="247"/>
+      <c r="V17" s="248"/>
     </row>
     <row r="18" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="195" t="s">
+      <c r="A18" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="196"/>
-      <c r="C18" s="196"/>
-      <c r="D18" s="197"/>
-      <c r="E18" s="225" t="s">
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="226"/>
-      <c r="G18" s="227"/>
-      <c r="H18" s="227"/>
-      <c r="I18" s="227"/>
-      <c r="J18" s="227"/>
-      <c r="K18" s="227"/>
-      <c r="L18" s="227"/>
-      <c r="M18" s="228"/>
-      <c r="N18" s="229" t="s">
+      <c r="F18" s="218"/>
+      <c r="G18" s="219"/>
+      <c r="H18" s="219"/>
+      <c r="I18" s="219"/>
+      <c r="J18" s="219"/>
+      <c r="K18" s="219"/>
+      <c r="L18" s="219"/>
+      <c r="M18" s="230"/>
+      <c r="N18" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O18" s="217"/>
-      <c r="P18" s="217"/>
-      <c r="Q18" s="218"/>
-      <c r="R18" s="234"/>
-      <c r="S18" s="235"/>
-      <c r="T18" s="235"/>
-      <c r="U18" s="235"/>
-      <c r="V18" s="236"/>
+      <c r="O18" s="232"/>
+      <c r="P18" s="232"/>
+      <c r="Q18" s="233"/>
+      <c r="R18" s="240"/>
+      <c r="S18" s="241"/>
+      <c r="T18" s="241"/>
+      <c r="U18" s="241"/>
+      <c r="V18" s="242"/>
     </row>
     <row r="19" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="198"/>
-      <c r="B19" s="199"/>
-      <c r="C19" s="199"/>
-      <c r="D19" s="200"/>
-      <c r="E19" s="243"/>
-      <c r="F19" s="244"/>
-      <c r="G19" s="244"/>
-      <c r="H19" s="244"/>
-      <c r="I19" s="244"/>
-      <c r="J19" s="244"/>
-      <c r="K19" s="244"/>
-      <c r="L19" s="244"/>
-      <c r="M19" s="245"/>
-      <c r="N19" s="230"/>
-      <c r="O19" s="220"/>
-      <c r="P19" s="220"/>
-      <c r="Q19" s="221"/>
-      <c r="R19" s="237"/>
-      <c r="S19" s="238"/>
-      <c r="T19" s="238"/>
-      <c r="U19" s="238"/>
-      <c r="V19" s="239"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="221"/>
+      <c r="F19" s="222"/>
+      <c r="G19" s="222"/>
+      <c r="H19" s="222"/>
+      <c r="I19" s="222"/>
+      <c r="J19" s="222"/>
+      <c r="K19" s="222"/>
+      <c r="L19" s="222"/>
+      <c r="M19" s="249"/>
+      <c r="N19" s="234"/>
+      <c r="O19" s="235"/>
+      <c r="P19" s="235"/>
+      <c r="Q19" s="236"/>
+      <c r="R19" s="243"/>
+      <c r="S19" s="244"/>
+      <c r="T19" s="244"/>
+      <c r="U19" s="244"/>
+      <c r="V19" s="245"/>
     </row>
     <row r="20" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="201"/>
-      <c r="B20" s="202"/>
-      <c r="C20" s="202"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="246"/>
-      <c r="F20" s="247"/>
-      <c r="G20" s="247"/>
-      <c r="H20" s="247"/>
-      <c r="I20" s="247"/>
-      <c r="J20" s="247"/>
-      <c r="K20" s="247"/>
-      <c r="L20" s="247"/>
-      <c r="M20" s="248"/>
-      <c r="N20" s="231"/>
-      <c r="O20" s="232"/>
-      <c r="P20" s="232"/>
-      <c r="Q20" s="233"/>
-      <c r="R20" s="240"/>
-      <c r="S20" s="241"/>
-      <c r="T20" s="241"/>
-      <c r="U20" s="241"/>
-      <c r="V20" s="242"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="227"/>
+      <c r="F20" s="228"/>
+      <c r="G20" s="228"/>
+      <c r="H20" s="228"/>
+      <c r="I20" s="228"/>
+      <c r="J20" s="228"/>
+      <c r="K20" s="228"/>
+      <c r="L20" s="228"/>
+      <c r="M20" s="250"/>
+      <c r="N20" s="237"/>
+      <c r="O20" s="238"/>
+      <c r="P20" s="238"/>
+      <c r="Q20" s="239"/>
+      <c r="R20" s="246"/>
+      <c r="S20" s="247"/>
+      <c r="T20" s="247"/>
+      <c r="U20" s="247"/>
+      <c r="V20" s="248"/>
     </row>
     <row r="21" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="195" t="s">
+      <c r="A21" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="217"/>
-      <c r="C21" s="217"/>
-      <c r="D21" s="218"/>
-      <c r="E21" s="225" t="s">
+      <c r="B21" s="232"/>
+      <c r="C21" s="232"/>
+      <c r="D21" s="233"/>
+      <c r="E21" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="226"/>
-      <c r="G21" s="227"/>
-      <c r="H21" s="227"/>
-      <c r="I21" s="227"/>
-      <c r="J21" s="227"/>
-      <c r="K21" s="227"/>
-      <c r="L21" s="227"/>
-      <c r="M21" s="228"/>
-      <c r="N21" s="229" t="s">
+      <c r="F21" s="218"/>
+      <c r="G21" s="219"/>
+      <c r="H21" s="219"/>
+      <c r="I21" s="219"/>
+      <c r="J21" s="219"/>
+      <c r="K21" s="219"/>
+      <c r="L21" s="219"/>
+      <c r="M21" s="230"/>
+      <c r="N21" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O21" s="217"/>
-      <c r="P21" s="217"/>
-      <c r="Q21" s="218"/>
-      <c r="R21" s="234"/>
-      <c r="S21" s="235"/>
-      <c r="T21" s="235"/>
-      <c r="U21" s="235"/>
-      <c r="V21" s="236"/>
+      <c r="O21" s="232"/>
+      <c r="P21" s="232"/>
+      <c r="Q21" s="233"/>
+      <c r="R21" s="240"/>
+      <c r="S21" s="241"/>
+      <c r="T21" s="241"/>
+      <c r="U21" s="241"/>
+      <c r="V21" s="242"/>
     </row>
     <row r="22" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="219"/>
-      <c r="B22" s="220"/>
-      <c r="C22" s="220"/>
-      <c r="D22" s="221"/>
-      <c r="E22" s="243"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
-      <c r="K22" s="244"/>
-      <c r="L22" s="244"/>
-      <c r="M22" s="245"/>
-      <c r="N22" s="230"/>
-      <c r="O22" s="220"/>
-      <c r="P22" s="220"/>
-      <c r="Q22" s="221"/>
-      <c r="R22" s="237"/>
-      <c r="S22" s="238"/>
-      <c r="T22" s="238"/>
-      <c r="U22" s="238"/>
-      <c r="V22" s="239"/>
+      <c r="A22" s="251"/>
+      <c r="B22" s="235"/>
+      <c r="C22" s="235"/>
+      <c r="D22" s="236"/>
+      <c r="E22" s="221"/>
+      <c r="F22" s="222"/>
+      <c r="G22" s="222"/>
+      <c r="H22" s="222"/>
+      <c r="I22" s="222"/>
+      <c r="J22" s="222"/>
+      <c r="K22" s="222"/>
+      <c r="L22" s="222"/>
+      <c r="M22" s="249"/>
+      <c r="N22" s="234"/>
+      <c r="O22" s="235"/>
+      <c r="P22" s="235"/>
+      <c r="Q22" s="236"/>
+      <c r="R22" s="243"/>
+      <c r="S22" s="244"/>
+      <c r="T22" s="244"/>
+      <c r="U22" s="244"/>
+      <c r="V22" s="245"/>
     </row>
     <row r="23" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="222"/>
-      <c r="B23" s="223"/>
-      <c r="C23" s="223"/>
-      <c r="D23" s="224"/>
-      <c r="E23" s="246"/>
-      <c r="F23" s="247"/>
-      <c r="G23" s="247"/>
-      <c r="H23" s="247"/>
-      <c r="I23" s="247"/>
-      <c r="J23" s="247"/>
-      <c r="K23" s="247"/>
-      <c r="L23" s="247"/>
-      <c r="M23" s="248"/>
-      <c r="N23" s="231"/>
-      <c r="O23" s="232"/>
-      <c r="P23" s="232"/>
-      <c r="Q23" s="233"/>
-      <c r="R23" s="240"/>
-      <c r="S23" s="241"/>
-      <c r="T23" s="241"/>
-      <c r="U23" s="241"/>
-      <c r="V23" s="242"/>
+      <c r="A23" s="252"/>
+      <c r="B23" s="253"/>
+      <c r="C23" s="253"/>
+      <c r="D23" s="254"/>
+      <c r="E23" s="227"/>
+      <c r="F23" s="228"/>
+      <c r="G23" s="228"/>
+      <c r="H23" s="228"/>
+      <c r="I23" s="228"/>
+      <c r="J23" s="228"/>
+      <c r="K23" s="228"/>
+      <c r="L23" s="228"/>
+      <c r="M23" s="250"/>
+      <c r="N23" s="237"/>
+      <c r="O23" s="238"/>
+      <c r="P23" s="238"/>
+      <c r="Q23" s="239"/>
+      <c r="R23" s="246"/>
+      <c r="S23" s="247"/>
+      <c r="T23" s="247"/>
+      <c r="U23" s="247"/>
+      <c r="V23" s="248"/>
     </row>
     <row r="24" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="195" t="s">
+      <c r="A24" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="217"/>
-      <c r="C24" s="217"/>
-      <c r="D24" s="218"/>
-      <c r="E24" s="225" t="s">
+      <c r="B24" s="232"/>
+      <c r="C24" s="232"/>
+      <c r="D24" s="233"/>
+      <c r="E24" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="226"/>
-      <c r="G24" s="227"/>
-      <c r="H24" s="227"/>
-      <c r="I24" s="227"/>
-      <c r="J24" s="227"/>
-      <c r="K24" s="227"/>
-      <c r="L24" s="227"/>
-      <c r="M24" s="228"/>
-      <c r="N24" s="229" t="s">
+      <c r="F24" s="218"/>
+      <c r="G24" s="219"/>
+      <c r="H24" s="219"/>
+      <c r="I24" s="219"/>
+      <c r="J24" s="219"/>
+      <c r="K24" s="219"/>
+      <c r="L24" s="219"/>
+      <c r="M24" s="230"/>
+      <c r="N24" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O24" s="217"/>
-      <c r="P24" s="217"/>
-      <c r="Q24" s="218"/>
-      <c r="R24" s="234"/>
-      <c r="S24" s="235"/>
-      <c r="T24" s="235"/>
-      <c r="U24" s="235"/>
-      <c r="V24" s="236"/>
+      <c r="O24" s="232"/>
+      <c r="P24" s="232"/>
+      <c r="Q24" s="233"/>
+      <c r="R24" s="240"/>
+      <c r="S24" s="241"/>
+      <c r="T24" s="241"/>
+      <c r="U24" s="241"/>
+      <c r="V24" s="242"/>
     </row>
     <row r="25" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="219"/>
-      <c r="B25" s="220"/>
-      <c r="C25" s="220"/>
-      <c r="D25" s="221"/>
-      <c r="E25" s="243"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
-      <c r="M25" s="245"/>
-      <c r="N25" s="230"/>
-      <c r="O25" s="220"/>
-      <c r="P25" s="220"/>
-      <c r="Q25" s="221"/>
-      <c r="R25" s="237"/>
-      <c r="S25" s="238"/>
-      <c r="T25" s="238"/>
-      <c r="U25" s="238"/>
-      <c r="V25" s="239"/>
+      <c r="A25" s="251"/>
+      <c r="B25" s="235"/>
+      <c r="C25" s="235"/>
+      <c r="D25" s="236"/>
+      <c r="E25" s="221"/>
+      <c r="F25" s="222"/>
+      <c r="G25" s="222"/>
+      <c r="H25" s="222"/>
+      <c r="I25" s="222"/>
+      <c r="J25" s="222"/>
+      <c r="K25" s="222"/>
+      <c r="L25" s="222"/>
+      <c r="M25" s="249"/>
+      <c r="N25" s="234"/>
+      <c r="O25" s="235"/>
+      <c r="P25" s="235"/>
+      <c r="Q25" s="236"/>
+      <c r="R25" s="243"/>
+      <c r="S25" s="244"/>
+      <c r="T25" s="244"/>
+      <c r="U25" s="244"/>
+      <c r="V25" s="245"/>
     </row>
     <row r="26" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="222"/>
-      <c r="B26" s="223"/>
-      <c r="C26" s="223"/>
-      <c r="D26" s="224"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="247"/>
-      <c r="G26" s="247"/>
-      <c r="H26" s="247"/>
-      <c r="I26" s="247"/>
-      <c r="J26" s="247"/>
-      <c r="K26" s="247"/>
-      <c r="L26" s="247"/>
-      <c r="M26" s="248"/>
-      <c r="N26" s="231"/>
-      <c r="O26" s="232"/>
-      <c r="P26" s="232"/>
-      <c r="Q26" s="233"/>
-      <c r="R26" s="240"/>
-      <c r="S26" s="241"/>
-      <c r="T26" s="241"/>
-      <c r="U26" s="241"/>
-      <c r="V26" s="242"/>
+      <c r="A26" s="252"/>
+      <c r="B26" s="253"/>
+      <c r="C26" s="253"/>
+      <c r="D26" s="254"/>
+      <c r="E26" s="227"/>
+      <c r="F26" s="228"/>
+      <c r="G26" s="228"/>
+      <c r="H26" s="228"/>
+      <c r="I26" s="228"/>
+      <c r="J26" s="228"/>
+      <c r="K26" s="228"/>
+      <c r="L26" s="228"/>
+      <c r="M26" s="250"/>
+      <c r="N26" s="237"/>
+      <c r="O26" s="238"/>
+      <c r="P26" s="238"/>
+      <c r="Q26" s="239"/>
+      <c r="R26" s="246"/>
+      <c r="S26" s="247"/>
+      <c r="T26" s="247"/>
+      <c r="U26" s="247"/>
+      <c r="V26" s="248"/>
     </row>
     <row r="27" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="195" t="s">
+      <c r="A27" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="217"/>
-      <c r="C27" s="217"/>
-      <c r="D27" s="218"/>
-      <c r="E27" s="225" t="s">
+      <c r="B27" s="232"/>
+      <c r="C27" s="232"/>
+      <c r="D27" s="233"/>
+      <c r="E27" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="226"/>
-      <c r="G27" s="227"/>
-      <c r="H27" s="227"/>
-      <c r="I27" s="227"/>
-      <c r="J27" s="227"/>
-      <c r="K27" s="227"/>
-      <c r="L27" s="227"/>
-      <c r="M27" s="228"/>
-      <c r="N27" s="229" t="s">
+      <c r="F27" s="218"/>
+      <c r="G27" s="219"/>
+      <c r="H27" s="219"/>
+      <c r="I27" s="219"/>
+      <c r="J27" s="219"/>
+      <c r="K27" s="219"/>
+      <c r="L27" s="219"/>
+      <c r="M27" s="230"/>
+      <c r="N27" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O27" s="217"/>
-      <c r="P27" s="217"/>
-      <c r="Q27" s="218"/>
-      <c r="R27" s="234"/>
-      <c r="S27" s="235"/>
-      <c r="T27" s="235"/>
-      <c r="U27" s="235"/>
-      <c r="V27" s="236"/>
+      <c r="O27" s="232"/>
+      <c r="P27" s="232"/>
+      <c r="Q27" s="233"/>
+      <c r="R27" s="240"/>
+      <c r="S27" s="241"/>
+      <c r="T27" s="241"/>
+      <c r="U27" s="241"/>
+      <c r="V27" s="242"/>
     </row>
     <row r="28" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="219"/>
-      <c r="B28" s="220"/>
-      <c r="C28" s="220"/>
-      <c r="D28" s="221"/>
-      <c r="E28" s="243"/>
-      <c r="F28" s="244"/>
-      <c r="G28" s="244"/>
-      <c r="H28" s="244"/>
-      <c r="I28" s="244"/>
-      <c r="J28" s="244"/>
-      <c r="K28" s="244"/>
-      <c r="L28" s="244"/>
-      <c r="M28" s="245"/>
-      <c r="N28" s="230"/>
-      <c r="O28" s="220"/>
-      <c r="P28" s="220"/>
-      <c r="Q28" s="221"/>
-      <c r="R28" s="237"/>
-      <c r="S28" s="238"/>
-      <c r="T28" s="238"/>
-      <c r="U28" s="238"/>
-      <c r="V28" s="239"/>
+      <c r="A28" s="251"/>
+      <c r="B28" s="235"/>
+      <c r="C28" s="235"/>
+      <c r="D28" s="236"/>
+      <c r="E28" s="221"/>
+      <c r="F28" s="222"/>
+      <c r="G28" s="222"/>
+      <c r="H28" s="222"/>
+      <c r="I28" s="222"/>
+      <c r="J28" s="222"/>
+      <c r="K28" s="222"/>
+      <c r="L28" s="222"/>
+      <c r="M28" s="249"/>
+      <c r="N28" s="234"/>
+      <c r="O28" s="235"/>
+      <c r="P28" s="235"/>
+      <c r="Q28" s="236"/>
+      <c r="R28" s="243"/>
+      <c r="S28" s="244"/>
+      <c r="T28" s="244"/>
+      <c r="U28" s="244"/>
+      <c r="V28" s="245"/>
     </row>
     <row r="29" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="222"/>
-      <c r="B29" s="223"/>
-      <c r="C29" s="223"/>
-      <c r="D29" s="224"/>
-      <c r="E29" s="246"/>
-      <c r="F29" s="247"/>
-      <c r="G29" s="247"/>
-      <c r="H29" s="247"/>
-      <c r="I29" s="247"/>
-      <c r="J29" s="247"/>
-      <c r="K29" s="247"/>
-      <c r="L29" s="247"/>
-      <c r="M29" s="248"/>
-      <c r="N29" s="231"/>
-      <c r="O29" s="232"/>
-      <c r="P29" s="232"/>
-      <c r="Q29" s="233"/>
-      <c r="R29" s="240"/>
-      <c r="S29" s="241"/>
-      <c r="T29" s="241"/>
-      <c r="U29" s="241"/>
-      <c r="V29" s="242"/>
+      <c r="A29" s="252"/>
+      <c r="B29" s="253"/>
+      <c r="C29" s="253"/>
+      <c r="D29" s="254"/>
+      <c r="E29" s="227"/>
+      <c r="F29" s="228"/>
+      <c r="G29" s="228"/>
+      <c r="H29" s="228"/>
+      <c r="I29" s="228"/>
+      <c r="J29" s="228"/>
+      <c r="K29" s="228"/>
+      <c r="L29" s="228"/>
+      <c r="M29" s="250"/>
+      <c r="N29" s="237"/>
+      <c r="O29" s="238"/>
+      <c r="P29" s="238"/>
+      <c r="Q29" s="239"/>
+      <c r="R29" s="246"/>
+      <c r="S29" s="247"/>
+      <c r="T29" s="247"/>
+      <c r="U29" s="247"/>
+      <c r="V29" s="248"/>
     </row>
     <row r="30" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="195" t="s">
+      <c r="A30" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="217"/>
-      <c r="C30" s="217"/>
-      <c r="D30" s="218"/>
-      <c r="E30" s="225" t="s">
+      <c r="B30" s="232"/>
+      <c r="C30" s="232"/>
+      <c r="D30" s="233"/>
+      <c r="E30" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="226"/>
-      <c r="G30" s="227"/>
-      <c r="H30" s="227"/>
-      <c r="I30" s="227"/>
-      <c r="J30" s="227"/>
-      <c r="K30" s="227"/>
-      <c r="L30" s="227"/>
-      <c r="M30" s="228"/>
-      <c r="N30" s="229" t="s">
+      <c r="F30" s="218"/>
+      <c r="G30" s="219"/>
+      <c r="H30" s="219"/>
+      <c r="I30" s="219"/>
+      <c r="J30" s="219"/>
+      <c r="K30" s="219"/>
+      <c r="L30" s="219"/>
+      <c r="M30" s="230"/>
+      <c r="N30" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O30" s="217"/>
-      <c r="P30" s="217"/>
-      <c r="Q30" s="218"/>
-      <c r="R30" s="234"/>
-      <c r="S30" s="235"/>
-      <c r="T30" s="235"/>
-      <c r="U30" s="235"/>
-      <c r="V30" s="236"/>
+      <c r="O30" s="232"/>
+      <c r="P30" s="232"/>
+      <c r="Q30" s="233"/>
+      <c r="R30" s="240"/>
+      <c r="S30" s="241"/>
+      <c r="T30" s="241"/>
+      <c r="U30" s="241"/>
+      <c r="V30" s="242"/>
     </row>
     <row r="31" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="219"/>
-      <c r="B31" s="220"/>
-      <c r="C31" s="220"/>
-      <c r="D31" s="221"/>
-      <c r="E31" s="243"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
-      <c r="M31" s="245"/>
-      <c r="N31" s="230"/>
-      <c r="O31" s="220"/>
-      <c r="P31" s="220"/>
-      <c r="Q31" s="221"/>
-      <c r="R31" s="237"/>
-      <c r="S31" s="238"/>
-      <c r="T31" s="238"/>
-      <c r="U31" s="238"/>
-      <c r="V31" s="239"/>
+      <c r="A31" s="251"/>
+      <c r="B31" s="235"/>
+      <c r="C31" s="235"/>
+      <c r="D31" s="236"/>
+      <c r="E31" s="221"/>
+      <c r="F31" s="222"/>
+      <c r="G31" s="222"/>
+      <c r="H31" s="222"/>
+      <c r="I31" s="222"/>
+      <c r="J31" s="222"/>
+      <c r="K31" s="222"/>
+      <c r="L31" s="222"/>
+      <c r="M31" s="249"/>
+      <c r="N31" s="234"/>
+      <c r="O31" s="235"/>
+      <c r="P31" s="235"/>
+      <c r="Q31" s="236"/>
+      <c r="R31" s="243"/>
+      <c r="S31" s="244"/>
+      <c r="T31" s="244"/>
+      <c r="U31" s="244"/>
+      <c r="V31" s="245"/>
     </row>
     <row r="32" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="222"/>
-      <c r="B32" s="223"/>
-      <c r="C32" s="223"/>
-      <c r="D32" s="224"/>
-      <c r="E32" s="246"/>
-      <c r="F32" s="247"/>
-      <c r="G32" s="247"/>
-      <c r="H32" s="247"/>
-      <c r="I32" s="247"/>
-      <c r="J32" s="247"/>
-      <c r="K32" s="247"/>
-      <c r="L32" s="247"/>
-      <c r="M32" s="248"/>
-      <c r="N32" s="231"/>
-      <c r="O32" s="232"/>
-      <c r="P32" s="232"/>
-      <c r="Q32" s="233"/>
-      <c r="R32" s="240"/>
-      <c r="S32" s="241"/>
-      <c r="T32" s="241"/>
-      <c r="U32" s="241"/>
-      <c r="V32" s="242"/>
+      <c r="A32" s="252"/>
+      <c r="B32" s="253"/>
+      <c r="C32" s="253"/>
+      <c r="D32" s="254"/>
+      <c r="E32" s="227"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="228"/>
+      <c r="H32" s="228"/>
+      <c r="I32" s="228"/>
+      <c r="J32" s="228"/>
+      <c r="K32" s="228"/>
+      <c r="L32" s="228"/>
+      <c r="M32" s="250"/>
+      <c r="N32" s="237"/>
+      <c r="O32" s="238"/>
+      <c r="P32" s="238"/>
+      <c r="Q32" s="239"/>
+      <c r="R32" s="246"/>
+      <c r="S32" s="247"/>
+      <c r="T32" s="247"/>
+      <c r="U32" s="247"/>
+      <c r="V32" s="248"/>
     </row>
     <row r="33" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="195" t="s">
+      <c r="A33" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="217"/>
-      <c r="C33" s="217"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="225" t="s">
+      <c r="B33" s="232"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="226"/>
-      <c r="G33" s="227"/>
-      <c r="H33" s="227"/>
-      <c r="I33" s="227"/>
-      <c r="J33" s="227"/>
-      <c r="K33" s="227"/>
-      <c r="L33" s="227"/>
-      <c r="M33" s="228"/>
-      <c r="N33" s="229" t="s">
+      <c r="F33" s="218"/>
+      <c r="G33" s="219"/>
+      <c r="H33" s="219"/>
+      <c r="I33" s="219"/>
+      <c r="J33" s="219"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
+      <c r="M33" s="230"/>
+      <c r="N33" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O33" s="217"/>
-      <c r="P33" s="217"/>
-      <c r="Q33" s="218"/>
-      <c r="R33" s="234"/>
-      <c r="S33" s="235"/>
-      <c r="T33" s="235"/>
-      <c r="U33" s="235"/>
-      <c r="V33" s="236"/>
+      <c r="O33" s="232"/>
+      <c r="P33" s="232"/>
+      <c r="Q33" s="233"/>
+      <c r="R33" s="240"/>
+      <c r="S33" s="241"/>
+      <c r="T33" s="241"/>
+      <c r="U33" s="241"/>
+      <c r="V33" s="242"/>
     </row>
     <row r="34" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="219"/>
-      <c r="B34" s="220"/>
-      <c r="C34" s="220"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="244"/>
-      <c r="G34" s="244"/>
-      <c r="H34" s="244"/>
-      <c r="I34" s="244"/>
-      <c r="J34" s="244"/>
-      <c r="K34" s="244"/>
-      <c r="L34" s="244"/>
-      <c r="M34" s="245"/>
-      <c r="N34" s="230"/>
-      <c r="O34" s="220"/>
-      <c r="P34" s="220"/>
-      <c r="Q34" s="221"/>
-      <c r="R34" s="237"/>
-      <c r="S34" s="238"/>
-      <c r="T34" s="238"/>
-      <c r="U34" s="238"/>
-      <c r="V34" s="239"/>
+      <c r="A34" s="251"/>
+      <c r="B34" s="235"/>
+      <c r="C34" s="235"/>
+      <c r="D34" s="236"/>
+      <c r="E34" s="221"/>
+      <c r="F34" s="222"/>
+      <c r="G34" s="222"/>
+      <c r="H34" s="222"/>
+      <c r="I34" s="222"/>
+      <c r="J34" s="222"/>
+      <c r="K34" s="222"/>
+      <c r="L34" s="222"/>
+      <c r="M34" s="249"/>
+      <c r="N34" s="234"/>
+      <c r="O34" s="235"/>
+      <c r="P34" s="235"/>
+      <c r="Q34" s="236"/>
+      <c r="R34" s="243"/>
+      <c r="S34" s="244"/>
+      <c r="T34" s="244"/>
+      <c r="U34" s="244"/>
+      <c r="V34" s="245"/>
     </row>
     <row r="35" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="222"/>
-      <c r="B35" s="223"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="246"/>
-      <c r="F35" s="247"/>
-      <c r="G35" s="247"/>
-      <c r="H35" s="247"/>
-      <c r="I35" s="247"/>
-      <c r="J35" s="247"/>
-      <c r="K35" s="247"/>
-      <c r="L35" s="247"/>
-      <c r="M35" s="248"/>
-      <c r="N35" s="231"/>
-      <c r="O35" s="232"/>
-      <c r="P35" s="232"/>
-      <c r="Q35" s="233"/>
-      <c r="R35" s="240"/>
-      <c r="S35" s="241"/>
-      <c r="T35" s="241"/>
-      <c r="U35" s="241"/>
-      <c r="V35" s="242"/>
+      <c r="A35" s="252"/>
+      <c r="B35" s="253"/>
+      <c r="C35" s="253"/>
+      <c r="D35" s="254"/>
+      <c r="E35" s="227"/>
+      <c r="F35" s="228"/>
+      <c r="G35" s="228"/>
+      <c r="H35" s="228"/>
+      <c r="I35" s="228"/>
+      <c r="J35" s="228"/>
+      <c r="K35" s="228"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="250"/>
+      <c r="N35" s="237"/>
+      <c r="O35" s="238"/>
+      <c r="P35" s="238"/>
+      <c r="Q35" s="239"/>
+      <c r="R35" s="246"/>
+      <c r="S35" s="247"/>
+      <c r="T35" s="247"/>
+      <c r="U35" s="247"/>
+      <c r="V35" s="248"/>
     </row>
     <row r="36" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="195" t="s">
+      <c r="A36" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="217"/>
-      <c r="C36" s="217"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="225" t="s">
+      <c r="B36" s="232"/>
+      <c r="C36" s="232"/>
+      <c r="D36" s="233"/>
+      <c r="E36" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="226"/>
-      <c r="G36" s="227"/>
-      <c r="H36" s="227"/>
-      <c r="I36" s="227"/>
-      <c r="J36" s="227"/>
-      <c r="K36" s="227"/>
-      <c r="L36" s="227"/>
-      <c r="M36" s="228"/>
-      <c r="N36" s="229" t="s">
+      <c r="F36" s="218"/>
+      <c r="G36" s="219"/>
+      <c r="H36" s="219"/>
+      <c r="I36" s="219"/>
+      <c r="J36" s="219"/>
+      <c r="K36" s="219"/>
+      <c r="L36" s="219"/>
+      <c r="M36" s="230"/>
+      <c r="N36" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O36" s="217"/>
-      <c r="P36" s="217"/>
-      <c r="Q36" s="218"/>
-      <c r="R36" s="234"/>
-      <c r="S36" s="235"/>
-      <c r="T36" s="235"/>
-      <c r="U36" s="235"/>
-      <c r="V36" s="236"/>
+      <c r="O36" s="232"/>
+      <c r="P36" s="232"/>
+      <c r="Q36" s="233"/>
+      <c r="R36" s="240"/>
+      <c r="S36" s="241"/>
+      <c r="T36" s="241"/>
+      <c r="U36" s="241"/>
+      <c r="V36" s="242"/>
     </row>
     <row r="37" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="219"/>
-      <c r="B37" s="220"/>
-      <c r="C37" s="220"/>
-      <c r="D37" s="221"/>
-      <c r="E37" s="243"/>
-      <c r="F37" s="244"/>
-      <c r="G37" s="244"/>
-      <c r="H37" s="244"/>
-      <c r="I37" s="244"/>
-      <c r="J37" s="244"/>
-      <c r="K37" s="244"/>
-      <c r="L37" s="244"/>
-      <c r="M37" s="245"/>
-      <c r="N37" s="230"/>
-      <c r="O37" s="220"/>
-      <c r="P37" s="220"/>
-      <c r="Q37" s="221"/>
-      <c r="R37" s="237"/>
-      <c r="S37" s="238"/>
-      <c r="T37" s="238"/>
-      <c r="U37" s="238"/>
-      <c r="V37" s="239"/>
+      <c r="A37" s="251"/>
+      <c r="B37" s="235"/>
+      <c r="C37" s="235"/>
+      <c r="D37" s="236"/>
+      <c r="E37" s="221"/>
+      <c r="F37" s="222"/>
+      <c r="G37" s="222"/>
+      <c r="H37" s="222"/>
+      <c r="I37" s="222"/>
+      <c r="J37" s="222"/>
+      <c r="K37" s="222"/>
+      <c r="L37" s="222"/>
+      <c r="M37" s="249"/>
+      <c r="N37" s="234"/>
+      <c r="O37" s="235"/>
+      <c r="P37" s="235"/>
+      <c r="Q37" s="236"/>
+      <c r="R37" s="243"/>
+      <c r="S37" s="244"/>
+      <c r="T37" s="244"/>
+      <c r="U37" s="244"/>
+      <c r="V37" s="245"/>
     </row>
     <row r="38" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="222"/>
-      <c r="B38" s="223"/>
-      <c r="C38" s="223"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="246"/>
-      <c r="F38" s="247"/>
-      <c r="G38" s="247"/>
-      <c r="H38" s="247"/>
-      <c r="I38" s="247"/>
-      <c r="J38" s="247"/>
-      <c r="K38" s="247"/>
-      <c r="L38" s="247"/>
-      <c r="M38" s="248"/>
-      <c r="N38" s="231"/>
-      <c r="O38" s="232"/>
-      <c r="P38" s="232"/>
-      <c r="Q38" s="233"/>
-      <c r="R38" s="240"/>
-      <c r="S38" s="241"/>
-      <c r="T38" s="241"/>
-      <c r="U38" s="241"/>
-      <c r="V38" s="242"/>
+      <c r="A38" s="252"/>
+      <c r="B38" s="253"/>
+      <c r="C38" s="253"/>
+      <c r="D38" s="254"/>
+      <c r="E38" s="227"/>
+      <c r="F38" s="228"/>
+      <c r="G38" s="228"/>
+      <c r="H38" s="228"/>
+      <c r="I38" s="228"/>
+      <c r="J38" s="228"/>
+      <c r="K38" s="228"/>
+      <c r="L38" s="228"/>
+      <c r="M38" s="250"/>
+      <c r="N38" s="237"/>
+      <c r="O38" s="238"/>
+      <c r="P38" s="238"/>
+      <c r="Q38" s="239"/>
+      <c r="R38" s="246"/>
+      <c r="S38" s="247"/>
+      <c r="T38" s="247"/>
+      <c r="U38" s="247"/>
+      <c r="V38" s="248"/>
     </row>
     <row r="39" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="195" t="s">
+      <c r="A39" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="217"/>
-      <c r="C39" s="217"/>
-      <c r="D39" s="218"/>
-      <c r="E39" s="225" t="s">
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F39" s="226"/>
-      <c r="G39" s="227"/>
-      <c r="H39" s="227"/>
-      <c r="I39" s="227"/>
-      <c r="J39" s="227"/>
-      <c r="K39" s="227"/>
-      <c r="L39" s="227"/>
-      <c r="M39" s="228"/>
-      <c r="N39" s="229" t="s">
+      <c r="F39" s="218"/>
+      <c r="G39" s="219"/>
+      <c r="H39" s="219"/>
+      <c r="I39" s="219"/>
+      <c r="J39" s="219"/>
+      <c r="K39" s="219"/>
+      <c r="L39" s="219"/>
+      <c r="M39" s="230"/>
+      <c r="N39" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O39" s="217"/>
-      <c r="P39" s="217"/>
-      <c r="Q39" s="218"/>
-      <c r="R39" s="234"/>
-      <c r="S39" s="235"/>
-      <c r="T39" s="235"/>
-      <c r="U39" s="235"/>
-      <c r="V39" s="236"/>
+      <c r="O39" s="232"/>
+      <c r="P39" s="232"/>
+      <c r="Q39" s="233"/>
+      <c r="R39" s="240"/>
+      <c r="S39" s="241"/>
+      <c r="T39" s="241"/>
+      <c r="U39" s="241"/>
+      <c r="V39" s="242"/>
     </row>
     <row r="40" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="219"/>
-      <c r="B40" s="220"/>
-      <c r="C40" s="220"/>
-      <c r="D40" s="221"/>
-      <c r="E40" s="243"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
-      <c r="M40" s="245"/>
-      <c r="N40" s="230"/>
-      <c r="O40" s="220"/>
-      <c r="P40" s="220"/>
-      <c r="Q40" s="221"/>
-      <c r="R40" s="237"/>
-      <c r="S40" s="238"/>
-      <c r="T40" s="238"/>
-      <c r="U40" s="238"/>
-      <c r="V40" s="239"/>
+      <c r="A40" s="251"/>
+      <c r="B40" s="235"/>
+      <c r="C40" s="235"/>
+      <c r="D40" s="236"/>
+      <c r="E40" s="221"/>
+      <c r="F40" s="222"/>
+      <c r="G40" s="222"/>
+      <c r="H40" s="222"/>
+      <c r="I40" s="222"/>
+      <c r="J40" s="222"/>
+      <c r="K40" s="222"/>
+      <c r="L40" s="222"/>
+      <c r="M40" s="249"/>
+      <c r="N40" s="234"/>
+      <c r="O40" s="235"/>
+      <c r="P40" s="235"/>
+      <c r="Q40" s="236"/>
+      <c r="R40" s="243"/>
+      <c r="S40" s="244"/>
+      <c r="T40" s="244"/>
+      <c r="U40" s="244"/>
+      <c r="V40" s="245"/>
     </row>
     <row r="41" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="222"/>
-      <c r="B41" s="223"/>
-      <c r="C41" s="223"/>
-      <c r="D41" s="224"/>
-      <c r="E41" s="246"/>
-      <c r="F41" s="247"/>
-      <c r="G41" s="247"/>
-      <c r="H41" s="247"/>
-      <c r="I41" s="247"/>
-      <c r="J41" s="247"/>
-      <c r="K41" s="247"/>
-      <c r="L41" s="247"/>
-      <c r="M41" s="248"/>
-      <c r="N41" s="231"/>
-      <c r="O41" s="232"/>
-      <c r="P41" s="232"/>
-      <c r="Q41" s="233"/>
-      <c r="R41" s="240"/>
-      <c r="S41" s="241"/>
-      <c r="T41" s="241"/>
-      <c r="U41" s="241"/>
-      <c r="V41" s="242"/>
+      <c r="A41" s="252"/>
+      <c r="B41" s="253"/>
+      <c r="C41" s="253"/>
+      <c r="D41" s="254"/>
+      <c r="E41" s="227"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="228"/>
+      <c r="H41" s="228"/>
+      <c r="I41" s="228"/>
+      <c r="J41" s="228"/>
+      <c r="K41" s="228"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="250"/>
+      <c r="N41" s="237"/>
+      <c r="O41" s="238"/>
+      <c r="P41" s="238"/>
+      <c r="Q41" s="239"/>
+      <c r="R41" s="246"/>
+      <c r="S41" s="247"/>
+      <c r="T41" s="247"/>
+      <c r="U41" s="247"/>
+      <c r="V41" s="248"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="195" t="s">
+      <c r="A42" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="217"/>
-      <c r="C42" s="217"/>
-      <c r="D42" s="218"/>
-      <c r="E42" s="225" t="s">
+      <c r="B42" s="232"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F42" s="226"/>
-      <c r="G42" s="227"/>
-      <c r="H42" s="227"/>
-      <c r="I42" s="227"/>
-      <c r="J42" s="227"/>
-      <c r="K42" s="227"/>
-      <c r="L42" s="227"/>
-      <c r="M42" s="228"/>
-      <c r="N42" s="229" t="s">
+      <c r="F42" s="218"/>
+      <c r="G42" s="219"/>
+      <c r="H42" s="219"/>
+      <c r="I42" s="219"/>
+      <c r="J42" s="219"/>
+      <c r="K42" s="219"/>
+      <c r="L42" s="219"/>
+      <c r="M42" s="230"/>
+      <c r="N42" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O42" s="217"/>
-      <c r="P42" s="217"/>
-      <c r="Q42" s="218"/>
-      <c r="R42" s="234"/>
-      <c r="S42" s="235"/>
-      <c r="T42" s="235"/>
-      <c r="U42" s="235"/>
-      <c r="V42" s="236"/>
+      <c r="O42" s="232"/>
+      <c r="P42" s="232"/>
+      <c r="Q42" s="233"/>
+      <c r="R42" s="240"/>
+      <c r="S42" s="241"/>
+      <c r="T42" s="241"/>
+      <c r="U42" s="241"/>
+      <c r="V42" s="242"/>
     </row>
     <row r="43" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="219"/>
-      <c r="B43" s="220"/>
-      <c r="C43" s="220"/>
-      <c r="D43" s="221"/>
-      <c r="E43" s="243"/>
-      <c r="F43" s="244"/>
-      <c r="G43" s="244"/>
-      <c r="H43" s="244"/>
-      <c r="I43" s="244"/>
-      <c r="J43" s="244"/>
-      <c r="K43" s="244"/>
-      <c r="L43" s="244"/>
-      <c r="M43" s="245"/>
-      <c r="N43" s="230"/>
-      <c r="O43" s="220"/>
-      <c r="P43" s="220"/>
-      <c r="Q43" s="221"/>
-      <c r="R43" s="237"/>
-      <c r="S43" s="238"/>
-      <c r="T43" s="238"/>
-      <c r="U43" s="238"/>
-      <c r="V43" s="239"/>
+      <c r="A43" s="251"/>
+      <c r="B43" s="235"/>
+      <c r="C43" s="235"/>
+      <c r="D43" s="236"/>
+      <c r="E43" s="221"/>
+      <c r="F43" s="222"/>
+      <c r="G43" s="222"/>
+      <c r="H43" s="222"/>
+      <c r="I43" s="222"/>
+      <c r="J43" s="222"/>
+      <c r="K43" s="222"/>
+      <c r="L43" s="222"/>
+      <c r="M43" s="249"/>
+      <c r="N43" s="234"/>
+      <c r="O43" s="235"/>
+      <c r="P43" s="235"/>
+      <c r="Q43" s="236"/>
+      <c r="R43" s="243"/>
+      <c r="S43" s="244"/>
+      <c r="T43" s="244"/>
+      <c r="U43" s="244"/>
+      <c r="V43" s="245"/>
     </row>
     <row r="44" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="222"/>
-      <c r="B44" s="223"/>
-      <c r="C44" s="223"/>
-      <c r="D44" s="224"/>
-      <c r="E44" s="246"/>
-      <c r="F44" s="247"/>
-      <c r="G44" s="247"/>
-      <c r="H44" s="247"/>
-      <c r="I44" s="247"/>
-      <c r="J44" s="247"/>
-      <c r="K44" s="247"/>
-      <c r="L44" s="247"/>
-      <c r="M44" s="248"/>
-      <c r="N44" s="231"/>
-      <c r="O44" s="232"/>
-      <c r="P44" s="232"/>
-      <c r="Q44" s="233"/>
-      <c r="R44" s="240"/>
-      <c r="S44" s="241"/>
-      <c r="T44" s="241"/>
-      <c r="U44" s="241"/>
-      <c r="V44" s="242"/>
+      <c r="A44" s="252"/>
+      <c r="B44" s="253"/>
+      <c r="C44" s="253"/>
+      <c r="D44" s="254"/>
+      <c r="E44" s="227"/>
+      <c r="F44" s="228"/>
+      <c r="G44" s="228"/>
+      <c r="H44" s="228"/>
+      <c r="I44" s="228"/>
+      <c r="J44" s="228"/>
+      <c r="K44" s="228"/>
+      <c r="L44" s="228"/>
+      <c r="M44" s="250"/>
+      <c r="N44" s="237"/>
+      <c r="O44" s="238"/>
+      <c r="P44" s="238"/>
+      <c r="Q44" s="239"/>
+      <c r="R44" s="246"/>
+      <c r="S44" s="247"/>
+      <c r="T44" s="247"/>
+      <c r="U44" s="247"/>
+      <c r="V44" s="248"/>
     </row>
     <row r="45" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="195" t="s">
+      <c r="A45" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="217"/>
-      <c r="C45" s="217"/>
-      <c r="D45" s="218"/>
-      <c r="E45" s="225" t="s">
+      <c r="B45" s="232"/>
+      <c r="C45" s="232"/>
+      <c r="D45" s="233"/>
+      <c r="E45" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F45" s="226"/>
-      <c r="G45" s="227"/>
-      <c r="H45" s="227"/>
-      <c r="I45" s="227"/>
-      <c r="J45" s="227"/>
-      <c r="K45" s="227"/>
-      <c r="L45" s="227"/>
-      <c r="M45" s="228"/>
-      <c r="N45" s="229" t="s">
+      <c r="F45" s="218"/>
+      <c r="G45" s="219"/>
+      <c r="H45" s="219"/>
+      <c r="I45" s="219"/>
+      <c r="J45" s="219"/>
+      <c r="K45" s="219"/>
+      <c r="L45" s="219"/>
+      <c r="M45" s="230"/>
+      <c r="N45" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O45" s="217"/>
-      <c r="P45" s="217"/>
-      <c r="Q45" s="218"/>
-      <c r="R45" s="234"/>
-      <c r="S45" s="235"/>
-      <c r="T45" s="235"/>
-      <c r="U45" s="235"/>
-      <c r="V45" s="236"/>
+      <c r="O45" s="232"/>
+      <c r="P45" s="232"/>
+      <c r="Q45" s="233"/>
+      <c r="R45" s="240"/>
+      <c r="S45" s="241"/>
+      <c r="T45" s="241"/>
+      <c r="U45" s="241"/>
+      <c r="V45" s="242"/>
     </row>
     <row r="46" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="219"/>
-      <c r="B46" s="220"/>
-      <c r="C46" s="220"/>
-      <c r="D46" s="221"/>
-      <c r="E46" s="243"/>
-      <c r="F46" s="244"/>
-      <c r="G46" s="244"/>
-      <c r="H46" s="244"/>
-      <c r="I46" s="244"/>
-      <c r="J46" s="244"/>
-      <c r="K46" s="244"/>
-      <c r="L46" s="244"/>
-      <c r="M46" s="245"/>
-      <c r="N46" s="230"/>
-      <c r="O46" s="220"/>
-      <c r="P46" s="220"/>
-      <c r="Q46" s="221"/>
-      <c r="R46" s="237"/>
-      <c r="S46" s="238"/>
-      <c r="T46" s="238"/>
-      <c r="U46" s="238"/>
-      <c r="V46" s="239"/>
+      <c r="A46" s="251"/>
+      <c r="B46" s="235"/>
+      <c r="C46" s="235"/>
+      <c r="D46" s="236"/>
+      <c r="E46" s="221"/>
+      <c r="F46" s="222"/>
+      <c r="G46" s="222"/>
+      <c r="H46" s="222"/>
+      <c r="I46" s="222"/>
+      <c r="J46" s="222"/>
+      <c r="K46" s="222"/>
+      <c r="L46" s="222"/>
+      <c r="M46" s="249"/>
+      <c r="N46" s="234"/>
+      <c r="O46" s="235"/>
+      <c r="P46" s="235"/>
+      <c r="Q46" s="236"/>
+      <c r="R46" s="243"/>
+      <c r="S46" s="244"/>
+      <c r="T46" s="244"/>
+      <c r="U46" s="244"/>
+      <c r="V46" s="245"/>
     </row>
     <row r="47" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="222"/>
-      <c r="B47" s="223"/>
-      <c r="C47" s="223"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="246"/>
-      <c r="F47" s="247"/>
-      <c r="G47" s="247"/>
-      <c r="H47" s="247"/>
-      <c r="I47" s="247"/>
-      <c r="J47" s="247"/>
-      <c r="K47" s="247"/>
-      <c r="L47" s="247"/>
-      <c r="M47" s="248"/>
-      <c r="N47" s="231"/>
-      <c r="O47" s="232"/>
-      <c r="P47" s="232"/>
-      <c r="Q47" s="233"/>
-      <c r="R47" s="240"/>
-      <c r="S47" s="241"/>
-      <c r="T47" s="241"/>
-      <c r="U47" s="241"/>
-      <c r="V47" s="242"/>
+      <c r="A47" s="252"/>
+      <c r="B47" s="253"/>
+      <c r="C47" s="253"/>
+      <c r="D47" s="254"/>
+      <c r="E47" s="227"/>
+      <c r="F47" s="228"/>
+      <c r="G47" s="228"/>
+      <c r="H47" s="228"/>
+      <c r="I47" s="228"/>
+      <c r="J47" s="228"/>
+      <c r="K47" s="228"/>
+      <c r="L47" s="228"/>
+      <c r="M47" s="250"/>
+      <c r="N47" s="237"/>
+      <c r="O47" s="238"/>
+      <c r="P47" s="238"/>
+      <c r="Q47" s="239"/>
+      <c r="R47" s="246"/>
+      <c r="S47" s="247"/>
+      <c r="T47" s="247"/>
+      <c r="U47" s="247"/>
+      <c r="V47" s="248"/>
     </row>
     <row r="48" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="195" t="s">
+      <c r="A48" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="217"/>
-      <c r="C48" s="217"/>
-      <c r="D48" s="218"/>
-      <c r="E48" s="225" t="s">
+      <c r="B48" s="232"/>
+      <c r="C48" s="232"/>
+      <c r="D48" s="233"/>
+      <c r="E48" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F48" s="226"/>
-      <c r="G48" s="227"/>
-      <c r="H48" s="227"/>
-      <c r="I48" s="227"/>
-      <c r="J48" s="227"/>
-      <c r="K48" s="227"/>
-      <c r="L48" s="227"/>
-      <c r="M48" s="228"/>
-      <c r="N48" s="229" t="s">
+      <c r="F48" s="218"/>
+      <c r="G48" s="219"/>
+      <c r="H48" s="219"/>
+      <c r="I48" s="219"/>
+      <c r="J48" s="219"/>
+      <c r="K48" s="219"/>
+      <c r="L48" s="219"/>
+      <c r="M48" s="230"/>
+      <c r="N48" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O48" s="217"/>
-      <c r="P48" s="217"/>
-      <c r="Q48" s="218"/>
-      <c r="R48" s="234"/>
-      <c r="S48" s="235"/>
-      <c r="T48" s="235"/>
-      <c r="U48" s="235"/>
-      <c r="V48" s="236"/>
+      <c r="O48" s="232"/>
+      <c r="P48" s="232"/>
+      <c r="Q48" s="233"/>
+      <c r="R48" s="240"/>
+      <c r="S48" s="241"/>
+      <c r="T48" s="241"/>
+      <c r="U48" s="241"/>
+      <c r="V48" s="242"/>
     </row>
     <row r="49" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="219"/>
-      <c r="B49" s="220"/>
-      <c r="C49" s="220"/>
-      <c r="D49" s="221"/>
-      <c r="E49" s="243"/>
-      <c r="F49" s="244"/>
-      <c r="G49" s="244"/>
-      <c r="H49" s="244"/>
-      <c r="I49" s="244"/>
-      <c r="J49" s="244"/>
-      <c r="K49" s="244"/>
-      <c r="L49" s="244"/>
-      <c r="M49" s="245"/>
-      <c r="N49" s="230"/>
-      <c r="O49" s="220"/>
-      <c r="P49" s="220"/>
-      <c r="Q49" s="221"/>
-      <c r="R49" s="237"/>
-      <c r="S49" s="238"/>
-      <c r="T49" s="238"/>
-      <c r="U49" s="238"/>
-      <c r="V49" s="239"/>
+      <c r="A49" s="251"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="236"/>
+      <c r="E49" s="221"/>
+      <c r="F49" s="222"/>
+      <c r="G49" s="222"/>
+      <c r="H49" s="222"/>
+      <c r="I49" s="222"/>
+      <c r="J49" s="222"/>
+      <c r="K49" s="222"/>
+      <c r="L49" s="222"/>
+      <c r="M49" s="249"/>
+      <c r="N49" s="234"/>
+      <c r="O49" s="235"/>
+      <c r="P49" s="235"/>
+      <c r="Q49" s="236"/>
+      <c r="R49" s="243"/>
+      <c r="S49" s="244"/>
+      <c r="T49" s="244"/>
+      <c r="U49" s="244"/>
+      <c r="V49" s="245"/>
     </row>
     <row r="50" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="222"/>
-      <c r="B50" s="223"/>
-      <c r="C50" s="223"/>
-      <c r="D50" s="224"/>
-      <c r="E50" s="246"/>
-      <c r="F50" s="247"/>
-      <c r="G50" s="247"/>
-      <c r="H50" s="247"/>
-      <c r="I50" s="247"/>
-      <c r="J50" s="247"/>
-      <c r="K50" s="247"/>
-      <c r="L50" s="247"/>
-      <c r="M50" s="248"/>
-      <c r="N50" s="231"/>
-      <c r="O50" s="232"/>
-      <c r="P50" s="232"/>
-      <c r="Q50" s="233"/>
-      <c r="R50" s="240"/>
-      <c r="S50" s="241"/>
-      <c r="T50" s="241"/>
-      <c r="U50" s="241"/>
-      <c r="V50" s="242"/>
+      <c r="A50" s="252"/>
+      <c r="B50" s="253"/>
+      <c r="C50" s="253"/>
+      <c r="D50" s="254"/>
+      <c r="E50" s="227"/>
+      <c r="F50" s="228"/>
+      <c r="G50" s="228"/>
+      <c r="H50" s="228"/>
+      <c r="I50" s="228"/>
+      <c r="J50" s="228"/>
+      <c r="K50" s="228"/>
+      <c r="L50" s="228"/>
+      <c r="M50" s="250"/>
+      <c r="N50" s="237"/>
+      <c r="O50" s="238"/>
+      <c r="P50" s="238"/>
+      <c r="Q50" s="239"/>
+      <c r="R50" s="246"/>
+      <c r="S50" s="247"/>
+      <c r="T50" s="247"/>
+      <c r="U50" s="247"/>
+      <c r="V50" s="248"/>
     </row>
     <row r="51" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="195" t="s">
+      <c r="A51" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="B51" s="217"/>
-      <c r="C51" s="217"/>
-      <c r="D51" s="218"/>
-      <c r="E51" s="225" t="s">
+      <c r="B51" s="232"/>
+      <c r="C51" s="232"/>
+      <c r="D51" s="233"/>
+      <c r="E51" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F51" s="226"/>
-      <c r="G51" s="227"/>
-      <c r="H51" s="227"/>
-      <c r="I51" s="227"/>
-      <c r="J51" s="227"/>
-      <c r="K51" s="227"/>
-      <c r="L51" s="227"/>
-      <c r="M51" s="228"/>
-      <c r="N51" s="229" t="s">
+      <c r="F51" s="218"/>
+      <c r="G51" s="219"/>
+      <c r="H51" s="219"/>
+      <c r="I51" s="219"/>
+      <c r="J51" s="219"/>
+      <c r="K51" s="219"/>
+      <c r="L51" s="219"/>
+      <c r="M51" s="230"/>
+      <c r="N51" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O51" s="217"/>
-      <c r="P51" s="217"/>
-      <c r="Q51" s="218"/>
-      <c r="R51" s="234"/>
-      <c r="S51" s="235"/>
-      <c r="T51" s="235"/>
-      <c r="U51" s="235"/>
-      <c r="V51" s="236"/>
+      <c r="O51" s="232"/>
+      <c r="P51" s="232"/>
+      <c r="Q51" s="233"/>
+      <c r="R51" s="240"/>
+      <c r="S51" s="241"/>
+      <c r="T51" s="241"/>
+      <c r="U51" s="241"/>
+      <c r="V51" s="242"/>
     </row>
     <row r="52" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="219"/>
-      <c r="B52" s="220"/>
-      <c r="C52" s="220"/>
-      <c r="D52" s="221"/>
-      <c r="E52" s="243"/>
-      <c r="F52" s="244"/>
-      <c r="G52" s="244"/>
-      <c r="H52" s="244"/>
-      <c r="I52" s="244"/>
-      <c r="J52" s="244"/>
-      <c r="K52" s="244"/>
-      <c r="L52" s="244"/>
-      <c r="M52" s="245"/>
-      <c r="N52" s="230"/>
-      <c r="O52" s="220"/>
-      <c r="P52" s="220"/>
-      <c r="Q52" s="221"/>
-      <c r="R52" s="237"/>
-      <c r="S52" s="238"/>
-      <c r="T52" s="238"/>
-      <c r="U52" s="238"/>
-      <c r="V52" s="239"/>
+      <c r="A52" s="251"/>
+      <c r="B52" s="235"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="236"/>
+      <c r="E52" s="221"/>
+      <c r="F52" s="222"/>
+      <c r="G52" s="222"/>
+      <c r="H52" s="222"/>
+      <c r="I52" s="222"/>
+      <c r="J52" s="222"/>
+      <c r="K52" s="222"/>
+      <c r="L52" s="222"/>
+      <c r="M52" s="249"/>
+      <c r="N52" s="234"/>
+      <c r="O52" s="235"/>
+      <c r="P52" s="235"/>
+      <c r="Q52" s="236"/>
+      <c r="R52" s="243"/>
+      <c r="S52" s="244"/>
+      <c r="T52" s="244"/>
+      <c r="U52" s="244"/>
+      <c r="V52" s="245"/>
     </row>
     <row r="53" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="222"/>
-      <c r="B53" s="223"/>
-      <c r="C53" s="223"/>
-      <c r="D53" s="224"/>
-      <c r="E53" s="246"/>
-      <c r="F53" s="247"/>
-      <c r="G53" s="247"/>
-      <c r="H53" s="247"/>
-      <c r="I53" s="247"/>
-      <c r="J53" s="247"/>
-      <c r="K53" s="247"/>
-      <c r="L53" s="247"/>
-      <c r="M53" s="248"/>
-      <c r="N53" s="231"/>
-      <c r="O53" s="232"/>
-      <c r="P53" s="232"/>
-      <c r="Q53" s="233"/>
-      <c r="R53" s="240"/>
-      <c r="S53" s="241"/>
-      <c r="T53" s="241"/>
-      <c r="U53" s="241"/>
-      <c r="V53" s="242"/>
+      <c r="A53" s="252"/>
+      <c r="B53" s="253"/>
+      <c r="C53" s="253"/>
+      <c r="D53" s="254"/>
+      <c r="E53" s="227"/>
+      <c r="F53" s="228"/>
+      <c r="G53" s="228"/>
+      <c r="H53" s="228"/>
+      <c r="I53" s="228"/>
+      <c r="J53" s="228"/>
+      <c r="K53" s="228"/>
+      <c r="L53" s="228"/>
+      <c r="M53" s="250"/>
+      <c r="N53" s="237"/>
+      <c r="O53" s="238"/>
+      <c r="P53" s="238"/>
+      <c r="Q53" s="239"/>
+      <c r="R53" s="246"/>
+      <c r="S53" s="247"/>
+      <c r="T53" s="247"/>
+      <c r="U53" s="247"/>
+      <c r="V53" s="248"/>
     </row>
     <row r="54" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="195" t="s">
+      <c r="A54" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="217"/>
-      <c r="C54" s="217"/>
-      <c r="D54" s="218"/>
-      <c r="E54" s="225" t="s">
+      <c r="B54" s="232"/>
+      <c r="C54" s="232"/>
+      <c r="D54" s="233"/>
+      <c r="E54" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F54" s="226"/>
-      <c r="G54" s="227"/>
-      <c r="H54" s="227"/>
-      <c r="I54" s="227"/>
-      <c r="J54" s="227"/>
-      <c r="K54" s="227"/>
-      <c r="L54" s="227"/>
-      <c r="M54" s="228"/>
-      <c r="N54" s="229" t="s">
+      <c r="F54" s="218"/>
+      <c r="G54" s="219"/>
+      <c r="H54" s="219"/>
+      <c r="I54" s="219"/>
+      <c r="J54" s="219"/>
+      <c r="K54" s="219"/>
+      <c r="L54" s="219"/>
+      <c r="M54" s="230"/>
+      <c r="N54" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O54" s="217"/>
-      <c r="P54" s="217"/>
-      <c r="Q54" s="218"/>
-      <c r="R54" s="234"/>
-      <c r="S54" s="235"/>
-      <c r="T54" s="235"/>
-      <c r="U54" s="235"/>
-      <c r="V54" s="236"/>
+      <c r="O54" s="232"/>
+      <c r="P54" s="232"/>
+      <c r="Q54" s="233"/>
+      <c r="R54" s="240"/>
+      <c r="S54" s="241"/>
+      <c r="T54" s="241"/>
+      <c r="U54" s="241"/>
+      <c r="V54" s="242"/>
     </row>
     <row r="55" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="219"/>
-      <c r="B55" s="220"/>
-      <c r="C55" s="220"/>
-      <c r="D55" s="221"/>
-      <c r="E55" s="243"/>
-      <c r="F55" s="244"/>
-      <c r="G55" s="244"/>
-      <c r="H55" s="244"/>
-      <c r="I55" s="244"/>
-      <c r="J55" s="244"/>
-      <c r="K55" s="244"/>
-      <c r="L55" s="244"/>
-      <c r="M55" s="245"/>
-      <c r="N55" s="230"/>
-      <c r="O55" s="220"/>
-      <c r="P55" s="220"/>
-      <c r="Q55" s="221"/>
-      <c r="R55" s="237"/>
-      <c r="S55" s="238"/>
-      <c r="T55" s="238"/>
-      <c r="U55" s="238"/>
-      <c r="V55" s="239"/>
+      <c r="A55" s="251"/>
+      <c r="B55" s="235"/>
+      <c r="C55" s="235"/>
+      <c r="D55" s="236"/>
+      <c r="E55" s="221"/>
+      <c r="F55" s="222"/>
+      <c r="G55" s="222"/>
+      <c r="H55" s="222"/>
+      <c r="I55" s="222"/>
+      <c r="J55" s="222"/>
+      <c r="K55" s="222"/>
+      <c r="L55" s="222"/>
+      <c r="M55" s="249"/>
+      <c r="N55" s="234"/>
+      <c r="O55" s="235"/>
+      <c r="P55" s="235"/>
+      <c r="Q55" s="236"/>
+      <c r="R55" s="243"/>
+      <c r="S55" s="244"/>
+      <c r="T55" s="244"/>
+      <c r="U55" s="244"/>
+      <c r="V55" s="245"/>
     </row>
     <row r="56" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="222"/>
-      <c r="B56" s="223"/>
-      <c r="C56" s="223"/>
-      <c r="D56" s="224"/>
-      <c r="E56" s="246"/>
-      <c r="F56" s="247"/>
-      <c r="G56" s="247"/>
-      <c r="H56" s="247"/>
-      <c r="I56" s="247"/>
-      <c r="J56" s="247"/>
-      <c r="K56" s="247"/>
-      <c r="L56" s="247"/>
-      <c r="M56" s="248"/>
-      <c r="N56" s="231"/>
-      <c r="O56" s="232"/>
-      <c r="P56" s="232"/>
-      <c r="Q56" s="233"/>
-      <c r="R56" s="240"/>
-      <c r="S56" s="241"/>
-      <c r="T56" s="241"/>
-      <c r="U56" s="241"/>
-      <c r="V56" s="242"/>
+      <c r="A56" s="252"/>
+      <c r="B56" s="253"/>
+      <c r="C56" s="253"/>
+      <c r="D56" s="254"/>
+      <c r="E56" s="227"/>
+      <c r="F56" s="228"/>
+      <c r="G56" s="228"/>
+      <c r="H56" s="228"/>
+      <c r="I56" s="228"/>
+      <c r="J56" s="228"/>
+      <c r="K56" s="228"/>
+      <c r="L56" s="228"/>
+      <c r="M56" s="250"/>
+      <c r="N56" s="237"/>
+      <c r="O56" s="238"/>
+      <c r="P56" s="238"/>
+      <c r="Q56" s="239"/>
+      <c r="R56" s="246"/>
+      <c r="S56" s="247"/>
+      <c r="T56" s="247"/>
+      <c r="U56" s="247"/>
+      <c r="V56" s="248"/>
     </row>
     <row r="57" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="195" t="s">
+      <c r="A57" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="217"/>
-      <c r="C57" s="217"/>
-      <c r="D57" s="218"/>
-      <c r="E57" s="225" t="s">
+      <c r="B57" s="232"/>
+      <c r="C57" s="232"/>
+      <c r="D57" s="233"/>
+      <c r="E57" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F57" s="226"/>
-      <c r="G57" s="227"/>
-      <c r="H57" s="227"/>
-      <c r="I57" s="227"/>
-      <c r="J57" s="227"/>
-      <c r="K57" s="227"/>
-      <c r="L57" s="227"/>
-      <c r="M57" s="228"/>
-      <c r="N57" s="229" t="s">
+      <c r="F57" s="218"/>
+      <c r="G57" s="219"/>
+      <c r="H57" s="219"/>
+      <c r="I57" s="219"/>
+      <c r="J57" s="219"/>
+      <c r="K57" s="219"/>
+      <c r="L57" s="219"/>
+      <c r="M57" s="230"/>
+      <c r="N57" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O57" s="217"/>
-      <c r="P57" s="217"/>
-      <c r="Q57" s="218"/>
-      <c r="R57" s="234"/>
-      <c r="S57" s="235"/>
-      <c r="T57" s="235"/>
-      <c r="U57" s="235"/>
-      <c r="V57" s="236"/>
+      <c r="O57" s="232"/>
+      <c r="P57" s="232"/>
+      <c r="Q57" s="233"/>
+      <c r="R57" s="240"/>
+      <c r="S57" s="241"/>
+      <c r="T57" s="241"/>
+      <c r="U57" s="241"/>
+      <c r="V57" s="242"/>
     </row>
     <row r="58" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="219"/>
-      <c r="B58" s="220"/>
-      <c r="C58" s="220"/>
-      <c r="D58" s="221"/>
-      <c r="E58" s="243"/>
-      <c r="F58" s="244"/>
-      <c r="G58" s="244"/>
-      <c r="H58" s="244"/>
-      <c r="I58" s="244"/>
-      <c r="J58" s="244"/>
-      <c r="K58" s="244"/>
-      <c r="L58" s="244"/>
-      <c r="M58" s="245"/>
-      <c r="N58" s="230"/>
-      <c r="O58" s="220"/>
-      <c r="P58" s="220"/>
-      <c r="Q58" s="221"/>
-      <c r="R58" s="237"/>
-      <c r="S58" s="238"/>
-      <c r="T58" s="238"/>
-      <c r="U58" s="238"/>
-      <c r="V58" s="239"/>
+      <c r="A58" s="251"/>
+      <c r="B58" s="235"/>
+      <c r="C58" s="235"/>
+      <c r="D58" s="236"/>
+      <c r="E58" s="221"/>
+      <c r="F58" s="222"/>
+      <c r="G58" s="222"/>
+      <c r="H58" s="222"/>
+      <c r="I58" s="222"/>
+      <c r="J58" s="222"/>
+      <c r="K58" s="222"/>
+      <c r="L58" s="222"/>
+      <c r="M58" s="249"/>
+      <c r="N58" s="234"/>
+      <c r="O58" s="235"/>
+      <c r="P58" s="235"/>
+      <c r="Q58" s="236"/>
+      <c r="R58" s="243"/>
+      <c r="S58" s="244"/>
+      <c r="T58" s="244"/>
+      <c r="U58" s="244"/>
+      <c r="V58" s="245"/>
     </row>
     <row r="59" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="222"/>
-      <c r="B59" s="223"/>
-      <c r="C59" s="223"/>
-      <c r="D59" s="224"/>
-      <c r="E59" s="246"/>
-      <c r="F59" s="247"/>
-      <c r="G59" s="247"/>
-      <c r="H59" s="247"/>
-      <c r="I59" s="247"/>
-      <c r="J59" s="247"/>
-      <c r="K59" s="247"/>
-      <c r="L59" s="247"/>
-      <c r="M59" s="248"/>
-      <c r="N59" s="231"/>
-      <c r="O59" s="232"/>
-      <c r="P59" s="232"/>
-      <c r="Q59" s="233"/>
-      <c r="R59" s="240"/>
-      <c r="S59" s="241"/>
-      <c r="T59" s="241"/>
-      <c r="U59" s="241"/>
-      <c r="V59" s="242"/>
+      <c r="A59" s="252"/>
+      <c r="B59" s="253"/>
+      <c r="C59" s="253"/>
+      <c r="D59" s="254"/>
+      <c r="E59" s="227"/>
+      <c r="F59" s="228"/>
+      <c r="G59" s="228"/>
+      <c r="H59" s="228"/>
+      <c r="I59" s="228"/>
+      <c r="J59" s="228"/>
+      <c r="K59" s="228"/>
+      <c r="L59" s="228"/>
+      <c r="M59" s="250"/>
+      <c r="N59" s="237"/>
+      <c r="O59" s="238"/>
+      <c r="P59" s="238"/>
+      <c r="Q59" s="239"/>
+      <c r="R59" s="246"/>
+      <c r="S59" s="247"/>
+      <c r="T59" s="247"/>
+      <c r="U59" s="247"/>
+      <c r="V59" s="248"/>
     </row>
     <row r="60" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="195" t="s">
+      <c r="A60" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="217"/>
-      <c r="C60" s="217"/>
-      <c r="D60" s="218"/>
-      <c r="E60" s="225" t="s">
+      <c r="B60" s="232"/>
+      <c r="C60" s="232"/>
+      <c r="D60" s="233"/>
+      <c r="E60" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F60" s="226"/>
-      <c r="G60" s="227"/>
-      <c r="H60" s="227"/>
-      <c r="I60" s="227"/>
-      <c r="J60" s="227"/>
-      <c r="K60" s="227"/>
-      <c r="L60" s="227"/>
-      <c r="M60" s="228"/>
-      <c r="N60" s="229" t="s">
+      <c r="F60" s="218"/>
+      <c r="G60" s="219"/>
+      <c r="H60" s="219"/>
+      <c r="I60" s="219"/>
+      <c r="J60" s="219"/>
+      <c r="K60" s="219"/>
+      <c r="L60" s="219"/>
+      <c r="M60" s="230"/>
+      <c r="N60" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O60" s="217"/>
-      <c r="P60" s="217"/>
-      <c r="Q60" s="218"/>
-      <c r="R60" s="234"/>
-      <c r="S60" s="235"/>
-      <c r="T60" s="235"/>
-      <c r="U60" s="235"/>
-      <c r="V60" s="236"/>
+      <c r="O60" s="232"/>
+      <c r="P60" s="232"/>
+      <c r="Q60" s="233"/>
+      <c r="R60" s="240"/>
+      <c r="S60" s="241"/>
+      <c r="T60" s="241"/>
+      <c r="U60" s="241"/>
+      <c r="V60" s="242"/>
     </row>
     <row r="61" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="219"/>
-      <c r="B61" s="220"/>
-      <c r="C61" s="220"/>
-      <c r="D61" s="221"/>
-      <c r="E61" s="243"/>
-      <c r="F61" s="244"/>
-      <c r="G61" s="244"/>
-      <c r="H61" s="244"/>
-      <c r="I61" s="244"/>
-      <c r="J61" s="244"/>
-      <c r="K61" s="244"/>
-      <c r="L61" s="244"/>
-      <c r="M61" s="245"/>
-      <c r="N61" s="230"/>
-      <c r="O61" s="220"/>
-      <c r="P61" s="220"/>
-      <c r="Q61" s="221"/>
-      <c r="R61" s="237"/>
-      <c r="S61" s="238"/>
-      <c r="T61" s="238"/>
-      <c r="U61" s="238"/>
-      <c r="V61" s="239"/>
+      <c r="A61" s="251"/>
+      <c r="B61" s="235"/>
+      <c r="C61" s="235"/>
+      <c r="D61" s="236"/>
+      <c r="E61" s="221"/>
+      <c r="F61" s="222"/>
+      <c r="G61" s="222"/>
+      <c r="H61" s="222"/>
+      <c r="I61" s="222"/>
+      <c r="J61" s="222"/>
+      <c r="K61" s="222"/>
+      <c r="L61" s="222"/>
+      <c r="M61" s="249"/>
+      <c r="N61" s="234"/>
+      <c r="O61" s="235"/>
+      <c r="P61" s="235"/>
+      <c r="Q61" s="236"/>
+      <c r="R61" s="243"/>
+      <c r="S61" s="244"/>
+      <c r="T61" s="244"/>
+      <c r="U61" s="244"/>
+      <c r="V61" s="245"/>
     </row>
     <row r="62" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="222"/>
-      <c r="B62" s="223"/>
-      <c r="C62" s="223"/>
-      <c r="D62" s="224"/>
-      <c r="E62" s="246"/>
-      <c r="F62" s="247"/>
-      <c r="G62" s="247"/>
-      <c r="H62" s="247"/>
-      <c r="I62" s="247"/>
-      <c r="J62" s="247"/>
-      <c r="K62" s="247"/>
-      <c r="L62" s="247"/>
-      <c r="M62" s="248"/>
-      <c r="N62" s="231"/>
-      <c r="O62" s="232"/>
-      <c r="P62" s="232"/>
-      <c r="Q62" s="233"/>
-      <c r="R62" s="240"/>
-      <c r="S62" s="241"/>
-      <c r="T62" s="241"/>
-      <c r="U62" s="241"/>
-      <c r="V62" s="242"/>
+      <c r="A62" s="252"/>
+      <c r="B62" s="253"/>
+      <c r="C62" s="253"/>
+      <c r="D62" s="254"/>
+      <c r="E62" s="227"/>
+      <c r="F62" s="228"/>
+      <c r="G62" s="228"/>
+      <c r="H62" s="228"/>
+      <c r="I62" s="228"/>
+      <c r="J62" s="228"/>
+      <c r="K62" s="228"/>
+      <c r="L62" s="228"/>
+      <c r="M62" s="250"/>
+      <c r="N62" s="237"/>
+      <c r="O62" s="238"/>
+      <c r="P62" s="238"/>
+      <c r="Q62" s="239"/>
+      <c r="R62" s="246"/>
+      <c r="S62" s="247"/>
+      <c r="T62" s="247"/>
+      <c r="U62" s="247"/>
+      <c r="V62" s="248"/>
     </row>
     <row r="63" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="195" t="s">
+      <c r="A63" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="B63" s="217"/>
-      <c r="C63" s="217"/>
-      <c r="D63" s="218"/>
-      <c r="E63" s="225" t="s">
+      <c r="B63" s="232"/>
+      <c r="C63" s="232"/>
+      <c r="D63" s="233"/>
+      <c r="E63" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F63" s="226"/>
-      <c r="G63" s="227"/>
-      <c r="H63" s="227"/>
-      <c r="I63" s="227"/>
-      <c r="J63" s="227"/>
-      <c r="K63" s="227"/>
-      <c r="L63" s="227"/>
-      <c r="M63" s="228"/>
-      <c r="N63" s="229" t="s">
+      <c r="F63" s="218"/>
+      <c r="G63" s="219"/>
+      <c r="H63" s="219"/>
+      <c r="I63" s="219"/>
+      <c r="J63" s="219"/>
+      <c r="K63" s="219"/>
+      <c r="L63" s="219"/>
+      <c r="M63" s="230"/>
+      <c r="N63" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O63" s="217"/>
-      <c r="P63" s="217"/>
-      <c r="Q63" s="218"/>
-      <c r="R63" s="234"/>
-      <c r="S63" s="235"/>
-      <c r="T63" s="235"/>
-      <c r="U63" s="235"/>
-      <c r="V63" s="236"/>
+      <c r="O63" s="232"/>
+      <c r="P63" s="232"/>
+      <c r="Q63" s="233"/>
+      <c r="R63" s="240"/>
+      <c r="S63" s="241"/>
+      <c r="T63" s="241"/>
+      <c r="U63" s="241"/>
+      <c r="V63" s="242"/>
     </row>
     <row r="64" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="219"/>
-      <c r="B64" s="220"/>
-      <c r="C64" s="220"/>
-      <c r="D64" s="221"/>
-      <c r="E64" s="243"/>
-      <c r="F64" s="244"/>
-      <c r="G64" s="244"/>
-      <c r="H64" s="244"/>
-      <c r="I64" s="244"/>
-      <c r="J64" s="244"/>
-      <c r="K64" s="244"/>
-      <c r="L64" s="244"/>
-      <c r="M64" s="245"/>
-      <c r="N64" s="230"/>
-      <c r="O64" s="220"/>
-      <c r="P64" s="220"/>
-      <c r="Q64" s="221"/>
-      <c r="R64" s="237"/>
-      <c r="S64" s="238"/>
-      <c r="T64" s="238"/>
-      <c r="U64" s="238"/>
-      <c r="V64" s="239"/>
+      <c r="A64" s="251"/>
+      <c r="B64" s="235"/>
+      <c r="C64" s="235"/>
+      <c r="D64" s="236"/>
+      <c r="E64" s="221"/>
+      <c r="F64" s="222"/>
+      <c r="G64" s="222"/>
+      <c r="H64" s="222"/>
+      <c r="I64" s="222"/>
+      <c r="J64" s="222"/>
+      <c r="K64" s="222"/>
+      <c r="L64" s="222"/>
+      <c r="M64" s="249"/>
+      <c r="N64" s="234"/>
+      <c r="O64" s="235"/>
+      <c r="P64" s="235"/>
+      <c r="Q64" s="236"/>
+      <c r="R64" s="243"/>
+      <c r="S64" s="244"/>
+      <c r="T64" s="244"/>
+      <c r="U64" s="244"/>
+      <c r="V64" s="245"/>
     </row>
     <row r="65" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="222"/>
-      <c r="B65" s="223"/>
-      <c r="C65" s="223"/>
-      <c r="D65" s="224"/>
-      <c r="E65" s="246"/>
-      <c r="F65" s="247"/>
-      <c r="G65" s="247"/>
-      <c r="H65" s="247"/>
-      <c r="I65" s="247"/>
-      <c r="J65" s="247"/>
-      <c r="K65" s="247"/>
-      <c r="L65" s="247"/>
-      <c r="M65" s="248"/>
-      <c r="N65" s="231"/>
-      <c r="O65" s="232"/>
-      <c r="P65" s="232"/>
-      <c r="Q65" s="233"/>
-      <c r="R65" s="240"/>
-      <c r="S65" s="241"/>
-      <c r="T65" s="241"/>
-      <c r="U65" s="241"/>
-      <c r="V65" s="242"/>
+      <c r="A65" s="252"/>
+      <c r="B65" s="253"/>
+      <c r="C65" s="253"/>
+      <c r="D65" s="254"/>
+      <c r="E65" s="227"/>
+      <c r="F65" s="228"/>
+      <c r="G65" s="228"/>
+      <c r="H65" s="228"/>
+      <c r="I65" s="228"/>
+      <c r="J65" s="228"/>
+      <c r="K65" s="228"/>
+      <c r="L65" s="228"/>
+      <c r="M65" s="250"/>
+      <c r="N65" s="237"/>
+      <c r="O65" s="238"/>
+      <c r="P65" s="238"/>
+      <c r="Q65" s="239"/>
+      <c r="R65" s="246"/>
+      <c r="S65" s="247"/>
+      <c r="T65" s="247"/>
+      <c r="U65" s="247"/>
+      <c r="V65" s="248"/>
     </row>
     <row r="66" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="195" t="s">
+      <c r="A66" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B66" s="217"/>
-      <c r="C66" s="217"/>
-      <c r="D66" s="218"/>
-      <c r="E66" s="225" t="s">
+      <c r="B66" s="232"/>
+      <c r="C66" s="232"/>
+      <c r="D66" s="233"/>
+      <c r="E66" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F66" s="226"/>
-      <c r="G66" s="227"/>
-      <c r="H66" s="227"/>
-      <c r="I66" s="227"/>
-      <c r="J66" s="227"/>
-      <c r="K66" s="227"/>
-      <c r="L66" s="227"/>
-      <c r="M66" s="228"/>
-      <c r="N66" s="229" t="s">
+      <c r="F66" s="218"/>
+      <c r="G66" s="219"/>
+      <c r="H66" s="219"/>
+      <c r="I66" s="219"/>
+      <c r="J66" s="219"/>
+      <c r="K66" s="219"/>
+      <c r="L66" s="219"/>
+      <c r="M66" s="230"/>
+      <c r="N66" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O66" s="217"/>
-      <c r="P66" s="217"/>
-      <c r="Q66" s="218"/>
-      <c r="R66" s="234"/>
-      <c r="S66" s="235"/>
-      <c r="T66" s="235"/>
-      <c r="U66" s="235"/>
-      <c r="V66" s="236"/>
+      <c r="O66" s="232"/>
+      <c r="P66" s="232"/>
+      <c r="Q66" s="233"/>
+      <c r="R66" s="240"/>
+      <c r="S66" s="241"/>
+      <c r="T66" s="241"/>
+      <c r="U66" s="241"/>
+      <c r="V66" s="242"/>
     </row>
     <row r="67" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="219"/>
-      <c r="B67" s="220"/>
-      <c r="C67" s="220"/>
-      <c r="D67" s="221"/>
-      <c r="E67" s="243"/>
-      <c r="F67" s="244"/>
-      <c r="G67" s="244"/>
-      <c r="H67" s="244"/>
-      <c r="I67" s="244"/>
-      <c r="J67" s="244"/>
-      <c r="K67" s="244"/>
-      <c r="L67" s="244"/>
-      <c r="M67" s="245"/>
-      <c r="N67" s="230"/>
-      <c r="O67" s="220"/>
-      <c r="P67" s="220"/>
-      <c r="Q67" s="221"/>
-      <c r="R67" s="237"/>
-      <c r="S67" s="238"/>
-      <c r="T67" s="238"/>
-      <c r="U67" s="238"/>
-      <c r="V67" s="239"/>
+      <c r="A67" s="251"/>
+      <c r="B67" s="235"/>
+      <c r="C67" s="235"/>
+      <c r="D67" s="236"/>
+      <c r="E67" s="221"/>
+      <c r="F67" s="222"/>
+      <c r="G67" s="222"/>
+      <c r="H67" s="222"/>
+      <c r="I67" s="222"/>
+      <c r="J67" s="222"/>
+      <c r="K67" s="222"/>
+      <c r="L67" s="222"/>
+      <c r="M67" s="249"/>
+      <c r="N67" s="234"/>
+      <c r="O67" s="235"/>
+      <c r="P67" s="235"/>
+      <c r="Q67" s="236"/>
+      <c r="R67" s="243"/>
+      <c r="S67" s="244"/>
+      <c r="T67" s="244"/>
+      <c r="U67" s="244"/>
+      <c r="V67" s="245"/>
     </row>
     <row r="68" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="222"/>
-      <c r="B68" s="223"/>
-      <c r="C68" s="223"/>
-      <c r="D68" s="224"/>
-      <c r="E68" s="246"/>
-      <c r="F68" s="247"/>
-      <c r="G68" s="247"/>
-      <c r="H68" s="247"/>
-      <c r="I68" s="247"/>
-      <c r="J68" s="247"/>
-      <c r="K68" s="247"/>
-      <c r="L68" s="247"/>
-      <c r="M68" s="248"/>
-      <c r="N68" s="231"/>
-      <c r="O68" s="232"/>
-      <c r="P68" s="232"/>
-      <c r="Q68" s="233"/>
-      <c r="R68" s="240"/>
-      <c r="S68" s="241"/>
-      <c r="T68" s="241"/>
-      <c r="U68" s="241"/>
-      <c r="V68" s="242"/>
+      <c r="A68" s="252"/>
+      <c r="B68" s="253"/>
+      <c r="C68" s="253"/>
+      <c r="D68" s="254"/>
+      <c r="E68" s="227"/>
+      <c r="F68" s="228"/>
+      <c r="G68" s="228"/>
+      <c r="H68" s="228"/>
+      <c r="I68" s="228"/>
+      <c r="J68" s="228"/>
+      <c r="K68" s="228"/>
+      <c r="L68" s="228"/>
+      <c r="M68" s="250"/>
+      <c r="N68" s="237"/>
+      <c r="O68" s="238"/>
+      <c r="P68" s="238"/>
+      <c r="Q68" s="239"/>
+      <c r="R68" s="246"/>
+      <c r="S68" s="247"/>
+      <c r="T68" s="247"/>
+      <c r="U68" s="247"/>
+      <c r="V68" s="248"/>
     </row>
     <row r="69" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="195" t="s">
+      <c r="A69" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="B69" s="217"/>
-      <c r="C69" s="217"/>
-      <c r="D69" s="218"/>
-      <c r="E69" s="225" t="s">
+      <c r="B69" s="232"/>
+      <c r="C69" s="232"/>
+      <c r="D69" s="233"/>
+      <c r="E69" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F69" s="226"/>
-      <c r="G69" s="227"/>
-      <c r="H69" s="227"/>
-      <c r="I69" s="227"/>
-      <c r="J69" s="227"/>
-      <c r="K69" s="227"/>
-      <c r="L69" s="227"/>
-      <c r="M69" s="228"/>
-      <c r="N69" s="229" t="s">
+      <c r="F69" s="218"/>
+      <c r="G69" s="219"/>
+      <c r="H69" s="219"/>
+      <c r="I69" s="219"/>
+      <c r="J69" s="219"/>
+      <c r="K69" s="219"/>
+      <c r="L69" s="219"/>
+      <c r="M69" s="230"/>
+      <c r="N69" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O69" s="217"/>
-      <c r="P69" s="217"/>
-      <c r="Q69" s="218"/>
-      <c r="R69" s="234"/>
-      <c r="S69" s="235"/>
-      <c r="T69" s="235"/>
-      <c r="U69" s="235"/>
-      <c r="V69" s="236"/>
+      <c r="O69" s="232"/>
+      <c r="P69" s="232"/>
+      <c r="Q69" s="233"/>
+      <c r="R69" s="240"/>
+      <c r="S69" s="241"/>
+      <c r="T69" s="241"/>
+      <c r="U69" s="241"/>
+      <c r="V69" s="242"/>
     </row>
     <row r="70" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="219"/>
-      <c r="B70" s="220"/>
-      <c r="C70" s="220"/>
-      <c r="D70" s="221"/>
-      <c r="E70" s="243"/>
-      <c r="F70" s="244"/>
-      <c r="G70" s="244"/>
-      <c r="H70" s="244"/>
-      <c r="I70" s="244"/>
-      <c r="J70" s="244"/>
-      <c r="K70" s="244"/>
-      <c r="L70" s="244"/>
-      <c r="M70" s="245"/>
-      <c r="N70" s="230"/>
-      <c r="O70" s="220"/>
-      <c r="P70" s="220"/>
-      <c r="Q70" s="221"/>
-      <c r="R70" s="237"/>
-      <c r="S70" s="238"/>
-      <c r="T70" s="238"/>
-      <c r="U70" s="238"/>
-      <c r="V70" s="239"/>
+      <c r="A70" s="251"/>
+      <c r="B70" s="235"/>
+      <c r="C70" s="235"/>
+      <c r="D70" s="236"/>
+      <c r="E70" s="221"/>
+      <c r="F70" s="222"/>
+      <c r="G70" s="222"/>
+      <c r="H70" s="222"/>
+      <c r="I70" s="222"/>
+      <c r="J70" s="222"/>
+      <c r="K70" s="222"/>
+      <c r="L70" s="222"/>
+      <c r="M70" s="249"/>
+      <c r="N70" s="234"/>
+      <c r="O70" s="235"/>
+      <c r="P70" s="235"/>
+      <c r="Q70" s="236"/>
+      <c r="R70" s="243"/>
+      <c r="S70" s="244"/>
+      <c r="T70" s="244"/>
+      <c r="U70" s="244"/>
+      <c r="V70" s="245"/>
     </row>
     <row r="71" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="222"/>
-      <c r="B71" s="223"/>
-      <c r="C71" s="223"/>
-      <c r="D71" s="224"/>
-      <c r="E71" s="246"/>
-      <c r="F71" s="247"/>
-      <c r="G71" s="247"/>
-      <c r="H71" s="247"/>
-      <c r="I71" s="247"/>
-      <c r="J71" s="247"/>
-      <c r="K71" s="247"/>
-      <c r="L71" s="247"/>
-      <c r="M71" s="248"/>
-      <c r="N71" s="231"/>
-      <c r="O71" s="232"/>
-      <c r="P71" s="232"/>
-      <c r="Q71" s="233"/>
-      <c r="R71" s="240"/>
-      <c r="S71" s="241"/>
-      <c r="T71" s="241"/>
-      <c r="U71" s="241"/>
-      <c r="V71" s="242"/>
+      <c r="A71" s="252"/>
+      <c r="B71" s="253"/>
+      <c r="C71" s="253"/>
+      <c r="D71" s="254"/>
+      <c r="E71" s="227"/>
+      <c r="F71" s="228"/>
+      <c r="G71" s="228"/>
+      <c r="H71" s="228"/>
+      <c r="I71" s="228"/>
+      <c r="J71" s="228"/>
+      <c r="K71" s="228"/>
+      <c r="L71" s="228"/>
+      <c r="M71" s="250"/>
+      <c r="N71" s="237"/>
+      <c r="O71" s="238"/>
+      <c r="P71" s="238"/>
+      <c r="Q71" s="239"/>
+      <c r="R71" s="246"/>
+      <c r="S71" s="247"/>
+      <c r="T71" s="247"/>
+      <c r="U71" s="247"/>
+      <c r="V71" s="248"/>
     </row>
     <row r="72" spans="1:22" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="195" t="s">
+      <c r="A72" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="B72" s="217"/>
-      <c r="C72" s="217"/>
-      <c r="D72" s="218"/>
-      <c r="E72" s="225" t="s">
+      <c r="B72" s="232"/>
+      <c r="C72" s="232"/>
+      <c r="D72" s="233"/>
+      <c r="E72" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F72" s="226"/>
-      <c r="G72" s="227"/>
-      <c r="H72" s="227"/>
-      <c r="I72" s="227"/>
-      <c r="J72" s="227"/>
-      <c r="K72" s="227"/>
-      <c r="L72" s="227"/>
-      <c r="M72" s="228"/>
-      <c r="N72" s="229" t="s">
+      <c r="F72" s="218"/>
+      <c r="G72" s="219"/>
+      <c r="H72" s="219"/>
+      <c r="I72" s="219"/>
+      <c r="J72" s="219"/>
+      <c r="K72" s="219"/>
+      <c r="L72" s="219"/>
+      <c r="M72" s="230"/>
+      <c r="N72" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="O72" s="217"/>
-      <c r="P72" s="217"/>
-      <c r="Q72" s="218"/>
-      <c r="R72" s="234"/>
-      <c r="S72" s="235"/>
-      <c r="T72" s="235"/>
-      <c r="U72" s="235"/>
-      <c r="V72" s="236"/>
+      <c r="O72" s="232"/>
+      <c r="P72" s="232"/>
+      <c r="Q72" s="233"/>
+      <c r="R72" s="240"/>
+      <c r="S72" s="241"/>
+      <c r="T72" s="241"/>
+      <c r="U72" s="241"/>
+      <c r="V72" s="242"/>
     </row>
     <row r="73" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="219"/>
-      <c r="B73" s="220"/>
-      <c r="C73" s="220"/>
-      <c r="D73" s="221"/>
-      <c r="E73" s="243"/>
-      <c r="F73" s="244"/>
-      <c r="G73" s="244"/>
-      <c r="H73" s="244"/>
-      <c r="I73" s="244"/>
-      <c r="J73" s="244"/>
-      <c r="K73" s="244"/>
-      <c r="L73" s="244"/>
-      <c r="M73" s="245"/>
-      <c r="N73" s="230"/>
-      <c r="O73" s="220"/>
-      <c r="P73" s="220"/>
-      <c r="Q73" s="221"/>
-      <c r="R73" s="237"/>
-      <c r="S73" s="238"/>
-      <c r="T73" s="238"/>
-      <c r="U73" s="238"/>
-      <c r="V73" s="239"/>
+      <c r="A73" s="251"/>
+      <c r="B73" s="235"/>
+      <c r="C73" s="235"/>
+      <c r="D73" s="236"/>
+      <c r="E73" s="221"/>
+      <c r="F73" s="222"/>
+      <c r="G73" s="222"/>
+      <c r="H73" s="222"/>
+      <c r="I73" s="222"/>
+      <c r="J73" s="222"/>
+      <c r="K73" s="222"/>
+      <c r="L73" s="222"/>
+      <c r="M73" s="249"/>
+      <c r="N73" s="234"/>
+      <c r="O73" s="235"/>
+      <c r="P73" s="235"/>
+      <c r="Q73" s="236"/>
+      <c r="R73" s="243"/>
+      <c r="S73" s="244"/>
+      <c r="T73" s="244"/>
+      <c r="U73" s="244"/>
+      <c r="V73" s="245"/>
     </row>
     <row r="74" spans="1:22" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="249"/>
-      <c r="B74" s="232"/>
-      <c r="C74" s="232"/>
-      <c r="D74" s="233"/>
-      <c r="E74" s="246"/>
-      <c r="F74" s="247"/>
-      <c r="G74" s="247"/>
-      <c r="H74" s="247"/>
-      <c r="I74" s="247"/>
-      <c r="J74" s="247"/>
-      <c r="K74" s="247"/>
-      <c r="L74" s="247"/>
-      <c r="M74" s="248"/>
-      <c r="N74" s="231"/>
-      <c r="O74" s="232"/>
-      <c r="P74" s="232"/>
-      <c r="Q74" s="233"/>
-      <c r="R74" s="240"/>
-      <c r="S74" s="241"/>
-      <c r="T74" s="241"/>
-      <c r="U74" s="241"/>
-      <c r="V74" s="242"/>
+      <c r="A74" s="255"/>
+      <c r="B74" s="238"/>
+      <c r="C74" s="238"/>
+      <c r="D74" s="239"/>
+      <c r="E74" s="227"/>
+      <c r="F74" s="228"/>
+      <c r="G74" s="228"/>
+      <c r="H74" s="228"/>
+      <c r="I74" s="228"/>
+      <c r="J74" s="228"/>
+      <c r="K74" s="228"/>
+      <c r="L74" s="228"/>
+      <c r="M74" s="250"/>
+      <c r="N74" s="237"/>
+      <c r="O74" s="238"/>
+      <c r="P74" s="238"/>
+      <c r="Q74" s="239"/>
+      <c r="R74" s="246"/>
+      <c r="S74" s="247"/>
+      <c r="T74" s="247"/>
+      <c r="U74" s="247"/>
+      <c r="V74" s="248"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="R8LaSDVkVjO6vJYqdIgYXi0FSqluSgTehxhQLfxSymU84QZGykeyu74YR1J3cLFqwp8reJ69/uqQGVsFCqor8w==" saltValue="PqeKwuDH1YA7dHJybuCJ2Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="132">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="N4:V4"/>
-    <mergeCell ref="A5:D9"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:V5"/>
-    <mergeCell ref="E6:V9"/>
-    <mergeCell ref="A18:D20"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:M18"/>
-    <mergeCell ref="N18:Q20"/>
-    <mergeCell ref="A10:D14"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:V10"/>
-    <mergeCell ref="E11:V14"/>
-    <mergeCell ref="N15:Q17"/>
-    <mergeCell ref="A15:D17"/>
-    <mergeCell ref="R18:V20"/>
-    <mergeCell ref="E19:M20"/>
+    <mergeCell ref="A57:D59"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:M57"/>
+    <mergeCell ref="N57:Q59"/>
+    <mergeCell ref="R57:V59"/>
+    <mergeCell ref="E58:M59"/>
+    <mergeCell ref="A66:D68"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G66:M66"/>
+    <mergeCell ref="N66:Q68"/>
+    <mergeCell ref="R66:V68"/>
+    <mergeCell ref="E67:M68"/>
+    <mergeCell ref="A63:D65"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:M63"/>
+    <mergeCell ref="N63:Q65"/>
+    <mergeCell ref="R63:V65"/>
+    <mergeCell ref="E64:M65"/>
+    <mergeCell ref="A54:D56"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:M54"/>
+    <mergeCell ref="N54:Q56"/>
+    <mergeCell ref="R54:V56"/>
+    <mergeCell ref="E55:M56"/>
+    <mergeCell ref="A72:D74"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:M72"/>
+    <mergeCell ref="N72:Q74"/>
+    <mergeCell ref="R72:V74"/>
+    <mergeCell ref="E73:M74"/>
+    <mergeCell ref="A69:D71"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="G69:M69"/>
+    <mergeCell ref="N69:Q71"/>
+    <mergeCell ref="R69:V71"/>
+    <mergeCell ref="E70:M71"/>
+    <mergeCell ref="A60:D62"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:M60"/>
+    <mergeCell ref="N60:Q62"/>
+    <mergeCell ref="R60:V62"/>
+    <mergeCell ref="E61:M62"/>
+    <mergeCell ref="A51:D53"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="N51:Q53"/>
+    <mergeCell ref="R51:V53"/>
+    <mergeCell ref="E52:M53"/>
+    <mergeCell ref="A48:D50"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:M48"/>
+    <mergeCell ref="N48:Q50"/>
+    <mergeCell ref="R48:V50"/>
+    <mergeCell ref="E49:M50"/>
+    <mergeCell ref="A45:D47"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:M45"/>
+    <mergeCell ref="N45:Q47"/>
+    <mergeCell ref="R45:V47"/>
+    <mergeCell ref="E46:M47"/>
+    <mergeCell ref="R39:V41"/>
+    <mergeCell ref="E40:M41"/>
+    <mergeCell ref="A42:D44"/>
+    <mergeCell ref="G42:M42"/>
+    <mergeCell ref="N42:Q44"/>
+    <mergeCell ref="R42:V44"/>
+    <mergeCell ref="E43:M44"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="A39:D41"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:M39"/>
+    <mergeCell ref="N39:Q41"/>
+    <mergeCell ref="G27:M27"/>
+    <mergeCell ref="N27:Q29"/>
+    <mergeCell ref="R27:V29"/>
+    <mergeCell ref="E28:M29"/>
+    <mergeCell ref="N33:Q35"/>
+    <mergeCell ref="R33:V35"/>
+    <mergeCell ref="E34:M35"/>
+    <mergeCell ref="A36:D38"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:M36"/>
+    <mergeCell ref="N36:Q38"/>
+    <mergeCell ref="R36:V38"/>
+    <mergeCell ref="E37:M38"/>
+    <mergeCell ref="A33:D35"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:M33"/>
     <mergeCell ref="A21:D23"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="R15:V17"/>
@@ -7708,94 +7770,26 @@
     <mergeCell ref="E31:M32"/>
     <mergeCell ref="A27:D29"/>
     <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:M27"/>
-    <mergeCell ref="N27:Q29"/>
-    <mergeCell ref="R27:V29"/>
-    <mergeCell ref="E28:M29"/>
-    <mergeCell ref="N33:Q35"/>
-    <mergeCell ref="R33:V35"/>
-    <mergeCell ref="E34:M35"/>
-    <mergeCell ref="A36:D38"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:M36"/>
-    <mergeCell ref="N36:Q38"/>
-    <mergeCell ref="R36:V38"/>
-    <mergeCell ref="E37:M38"/>
-    <mergeCell ref="A33:D35"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:M33"/>
-    <mergeCell ref="A45:D47"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G45:M45"/>
-    <mergeCell ref="N45:Q47"/>
-    <mergeCell ref="R45:V47"/>
-    <mergeCell ref="E46:M47"/>
-    <mergeCell ref="R39:V41"/>
-    <mergeCell ref="E40:M41"/>
-    <mergeCell ref="A42:D44"/>
-    <mergeCell ref="G42:M42"/>
-    <mergeCell ref="N42:Q44"/>
-    <mergeCell ref="R42:V44"/>
-    <mergeCell ref="E43:M44"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A39:D41"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:M39"/>
-    <mergeCell ref="N39:Q41"/>
-    <mergeCell ref="A51:D53"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="G51:M51"/>
-    <mergeCell ref="N51:Q53"/>
-    <mergeCell ref="R51:V53"/>
-    <mergeCell ref="E52:M53"/>
-    <mergeCell ref="A48:D50"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="G48:M48"/>
-    <mergeCell ref="N48:Q50"/>
-    <mergeCell ref="R48:V50"/>
-    <mergeCell ref="E49:M50"/>
-    <mergeCell ref="A54:D56"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:M54"/>
-    <mergeCell ref="N54:Q56"/>
-    <mergeCell ref="R54:V56"/>
-    <mergeCell ref="E55:M56"/>
-    <mergeCell ref="A72:D74"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:M72"/>
-    <mergeCell ref="N72:Q74"/>
-    <mergeCell ref="R72:V74"/>
-    <mergeCell ref="E73:M74"/>
-    <mergeCell ref="A69:D71"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="G69:M69"/>
-    <mergeCell ref="N69:Q71"/>
-    <mergeCell ref="R69:V71"/>
-    <mergeCell ref="E70:M71"/>
-    <mergeCell ref="A60:D62"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G60:M60"/>
-    <mergeCell ref="N60:Q62"/>
-    <mergeCell ref="R60:V62"/>
-    <mergeCell ref="E61:M62"/>
-    <mergeCell ref="A57:D59"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:M57"/>
-    <mergeCell ref="N57:Q59"/>
-    <mergeCell ref="R57:V59"/>
-    <mergeCell ref="E58:M59"/>
-    <mergeCell ref="A66:D68"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="G66:M66"/>
-    <mergeCell ref="N66:Q68"/>
-    <mergeCell ref="R66:V68"/>
-    <mergeCell ref="E67:M68"/>
-    <mergeCell ref="A63:D65"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G63:M63"/>
-    <mergeCell ref="N63:Q65"/>
-    <mergeCell ref="R63:V65"/>
-    <mergeCell ref="E64:M65"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="A5:D9"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:V5"/>
+    <mergeCell ref="E6:V9"/>
+    <mergeCell ref="A18:D20"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:M18"/>
+    <mergeCell ref="N18:Q20"/>
+    <mergeCell ref="A10:D14"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:V10"/>
+    <mergeCell ref="E11:V14"/>
+    <mergeCell ref="N15:Q17"/>
+    <mergeCell ref="A15:D17"/>
+    <mergeCell ref="R18:V20"/>
+    <mergeCell ref="E19:M20"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7817,6 +7811,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010089C03295743358478A4F3419041186F3" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="25bc01c4799e0852f2b66931b3f23d84">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2dd3c506-0c5a-4c1a-a350-79afdbf97746" xmlns:ns3="e5f18f0f-c440-4f2f-8796-6fe2bf3ec072" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b991b2f23d9b33a33baff6a4b7c2717" ns2:_="" ns3:_="">
     <xsd:import namespace="2dd3c506-0c5a-4c1a-a350-79afdbf97746"/>
@@ -8011,15 +8014,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{313BB455-55A8-48BC-80EB-ADC73F21ED4A}">
   <ds:schemaRefs>
@@ -8032,6 +8026,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0CB8E4-968D-418F-9265-D930032B24BA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FC0466-D926-4B7C-8E95-125D74F21DEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8048,12 +8050,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0CB8E4-968D-418F-9265-D930032B24BA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>